--- a/Kapabilite/Kapabilite 2025.xlsx
+++ b/Kapabilite/Kapabilite 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yak\Desktop\Python\Kapabilite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF7F4574-C3C4-47D0-BE81-2D1D5A6E0BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9C0BB7-F0A3-4B95-8DBD-5B5BB01C6F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8FA9AADE-0AF1-42A7-AB4A-1A5F3041D90E}"/>
   </bookViews>
@@ -1021,7 +1021,7 @@
     <col min="75" max="79" width="9.7109375" style="3" customWidth="1"/>
     <col min="80" max="80" width="12.28515625" style="3" bestFit="1" customWidth="1"/>
     <col min="81" max="85" width="9.7109375" style="3" customWidth="1"/>
-    <col min="86" max="86" width="11.140625" style="11" customWidth="1"/>
+    <col min="86" max="86" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
     <col min="87" max="87" width="9.7109375" style="11" customWidth="1"/>
     <col min="88" max="91" width="9.7109375" style="3" customWidth="1"/>
     <col min="92" max="257" width="8.85546875" style="3"/>
@@ -3355,27 +3355,27 @@
       </c>
       <c r="N3" s="8">
         <f t="shared" ref="N3:N34" si="0">IFERROR(AVERAGE(T3,Z3,AF3,AL3,AR3,AX3,BD3,BJ3,BP3,BV3,CB3,CH3)," ")</f>
-        <v>50265.63636363636</v>
+        <v>48673.666666666664</v>
       </c>
       <c r="O3" s="8">
         <f t="shared" ref="O3:O34" si="1">IFERROR(AVERAGE(U3,AA3,AG3,AM3,AS3,AY3,BE3,BK3,BQ3,BW3,CC3,CI3)," ")</f>
-        <v>16068.454545454546</v>
+        <v>15645.166666666666</v>
       </c>
       <c r="P3" s="8">
         <f t="shared" ref="P3:P34" si="2">IFERROR(SUM(V3,AB3,AH3,AN3,AT3,AZ3,BF3,BL3,BR3,BX3,CD3,CJ3)," ")</f>
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Q3" s="9">
         <f t="shared" ref="Q3:Q34" si="3">IFERROR(SUM(T3,Z3,AF3,AL3,AR3,AX3,BD3,BJ3,BP3,BV3,CB3,CH3)/P3*3," ")</f>
-        <v>12107.78102189781</v>
+        <v>12084.496551724138</v>
       </c>
       <c r="R3" s="9">
         <f t="shared" ref="R3:R34" si="4">IFERROR(SUM(U3,AA3,AG3,AM3,AS3,AY3,BE3,BK3,BQ3,BW3,CC3,CI3)/P3*3," ")</f>
-        <v>3870.5036496350367</v>
+        <v>3884.31724137931</v>
       </c>
       <c r="S3" s="10">
         <f t="shared" ref="S3:S34" si="5">IFERROR(AVERAGE(Y3,AE3,AK3,AQ3,AW3,BC3,BI3,BO3,BU3,CA3,CG3,CM3)," ")</f>
-        <v>9.0798193173072193</v>
+        <v>9.0952251878795689</v>
       </c>
       <c r="T3" s="11">
         <v>14036</v>
@@ -3575,10 +3575,24 @@
       <c r="CG3" s="13">
         <v>8.0972351695689522</v>
       </c>
-      <c r="CJ3" s="11"/>
-      <c r="CK3" s="12"/>
-      <c r="CL3" s="12"/>
-      <c r="CM3" s="13"/>
+      <c r="CH3" s="11">
+        <v>31162</v>
+      </c>
+      <c r="CI3" s="11">
+        <v>10989</v>
+      </c>
+      <c r="CJ3" s="11">
+        <v>8</v>
+      </c>
+      <c r="CK3" s="12">
+        <v>11685.75</v>
+      </c>
+      <c r="CL3" s="12">
+        <v>4120.875</v>
+      </c>
+      <c r="CM3" s="13">
+        <v>9.2646897641754204</v>
+      </c>
     </row>
     <row r="4" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -3622,27 +3636,27 @@
       </c>
       <c r="N4" s="8">
         <f t="shared" si="0"/>
-        <v>270363.09090909088</v>
+        <v>273099.5</v>
       </c>
       <c r="O4" s="8">
         <f t="shared" si="1"/>
-        <v>10872.90909090909</v>
+        <v>10903.833333333334</v>
       </c>
       <c r="P4" s="8">
         <f t="shared" si="2"/>
-        <v>484</v>
+        <v>532</v>
       </c>
       <c r="Q4" s="9">
         <f t="shared" si="3"/>
-        <v>18433.847107438018</v>
+        <v>18480.417293233084</v>
       </c>
       <c r="R4" s="9">
         <f t="shared" si="4"/>
-        <v>741.33471074380168</v>
+        <v>737.85338345864659</v>
       </c>
       <c r="S4" s="10">
         <f t="shared" si="5"/>
-        <v>2.767811340657512</v>
+        <v>2.7579937289360523</v>
       </c>
       <c r="T4" s="11">
         <v>273196</v>
@@ -3842,10 +3856,24 @@
       <c r="CG4" s="13">
         <v>2.6488853990290941</v>
       </c>
-      <c r="CJ4" s="11"/>
-      <c r="CK4" s="12"/>
-      <c r="CL4" s="12"/>
-      <c r="CM4" s="13"/>
+      <c r="CH4" s="11">
+        <v>303200</v>
+      </c>
+      <c r="CI4" s="11">
+        <v>11244</v>
+      </c>
+      <c r="CJ4" s="11">
+        <v>48</v>
+      </c>
+      <c r="CK4" s="12">
+        <v>18950</v>
+      </c>
+      <c r="CL4" s="12">
+        <v>702.75</v>
+      </c>
+      <c r="CM4" s="13">
+        <v>2.65</v>
+      </c>
     </row>
     <row r="5" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -3889,27 +3917,27 @@
       </c>
       <c r="N5" s="8">
         <f t="shared" si="0"/>
-        <v>287173.27272727271</v>
+        <v>294407.16666666669</v>
       </c>
       <c r="O5" s="8">
         <f t="shared" si="1"/>
-        <v>12964.818181818182</v>
+        <v>13040.166666666666</v>
       </c>
       <c r="P5" s="8">
         <f t="shared" si="2"/>
-        <v>562</v>
+        <v>622</v>
       </c>
       <c r="Q5" s="9">
         <f t="shared" si="3"/>
-        <v>16862.487544483985</v>
+        <v>17039.643086816719</v>
       </c>
       <c r="R5" s="9">
         <f t="shared" si="4"/>
-        <v>761.27935943060493</v>
+        <v>754.7363344051447</v>
       </c>
       <c r="S5" s="10">
         <f t="shared" si="5"/>
-        <v>2.9805587990682425</v>
+        <v>2.9530122324792223</v>
       </c>
       <c r="T5" s="11">
         <v>303782</v>
@@ -4109,10 +4137,24 @@
       <c r="CG5" s="13">
         <v>2.806729002630957</v>
       </c>
-      <c r="CJ5" s="11"/>
-      <c r="CK5" s="12"/>
-      <c r="CL5" s="12"/>
-      <c r="CM5" s="13"/>
+      <c r="CH5" s="11">
+        <v>373980</v>
+      </c>
+      <c r="CI5" s="11">
+        <v>13869</v>
+      </c>
+      <c r="CJ5" s="11">
+        <v>60</v>
+      </c>
+      <c r="CK5" s="12">
+        <v>18699</v>
+      </c>
+      <c r="CL5" s="12">
+        <v>693.45</v>
+      </c>
+      <c r="CM5" s="13">
+        <v>2.65</v>
+      </c>
     </row>
     <row r="6" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
@@ -4156,27 +4198,27 @@
       </c>
       <c r="N6" s="8">
         <f t="shared" si="0"/>
-        <v>245606.09090909091</v>
+        <v>247638.75</v>
       </c>
       <c r="O6" s="8">
         <f t="shared" si="1"/>
-        <v>18773.454545454544</v>
+        <v>19191.75</v>
       </c>
       <c r="P6" s="8">
         <f t="shared" si="2"/>
-        <v>590</v>
+        <v>652</v>
       </c>
       <c r="Q6" s="9">
         <f t="shared" si="3"/>
-        <v>13737.289830508475</v>
+        <v>13673.305214723925</v>
       </c>
       <c r="R6" s="9">
         <f t="shared" si="4"/>
-        <v>1050.0406779661016</v>
+        <v>1059.6671779141104</v>
       </c>
       <c r="S6" s="10">
         <f t="shared" si="5"/>
-        <v>3.7625924391218875</v>
+        <v>3.7875438801294599</v>
       </c>
       <c r="T6" s="11">
         <v>210176</v>
@@ -4376,10 +4418,24 @@
       <c r="CG6" s="13">
         <v>4.0039334463025629</v>
       </c>
-      <c r="CJ6" s="11"/>
-      <c r="CK6" s="12"/>
-      <c r="CL6" s="12"/>
-      <c r="CM6" s="13"/>
+      <c r="CH6" s="11">
+        <v>269998</v>
+      </c>
+      <c r="CI6" s="11">
+        <v>23793</v>
+      </c>
+      <c r="CJ6" s="11">
+        <v>62</v>
+      </c>
+      <c r="CK6" s="12">
+        <v>13064.41935483871</v>
+      </c>
+      <c r="CL6" s="12">
+        <v>1151.2741935483871</v>
+      </c>
+      <c r="CM6" s="13">
+        <v>4.0620097312127514</v>
+      </c>
     </row>
     <row r="7" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
@@ -4423,27 +4479,27 @@
       </c>
       <c r="N7" s="8">
         <f t="shared" si="0"/>
-        <v>327433.45454545453</v>
+        <v>327918.58333333331</v>
       </c>
       <c r="O7" s="8">
         <f t="shared" si="1"/>
-        <v>51695.545454545456</v>
+        <v>52577.25</v>
       </c>
       <c r="P7" s="8">
         <f t="shared" si="2"/>
-        <v>651</v>
+        <v>715</v>
       </c>
       <c r="Q7" s="9">
         <f t="shared" si="3"/>
-        <v>16598.00921658986</v>
+        <v>16510.586013986016</v>
       </c>
       <c r="R7" s="9">
         <f t="shared" si="4"/>
-        <v>2620.5115207373269</v>
+        <v>2647.2461538461539</v>
       </c>
       <c r="S7" s="10">
         <f t="shared" si="5"/>
-        <v>5.3492653578059857</v>
+        <v>5.3949016432994767</v>
       </c>
       <c r="T7" s="11">
         <v>292850</v>
@@ -4643,10 +4699,24 @@
       <c r="CG7" s="13">
         <v>4.9653545095163922</v>
       </c>
-      <c r="CJ7" s="11"/>
-      <c r="CK7" s="12"/>
-      <c r="CL7" s="12"/>
-      <c r="CM7" s="13"/>
+      <c r="CH7" s="11">
+        <v>333255</v>
+      </c>
+      <c r="CI7" s="11">
+        <v>62276</v>
+      </c>
+      <c r="CJ7" s="11">
+        <v>64</v>
+      </c>
+      <c r="CK7" s="12">
+        <v>15621.328125</v>
+      </c>
+      <c r="CL7" s="12">
+        <v>2919.1875</v>
+      </c>
+      <c r="CM7" s="13">
+        <v>5.8969007837278804</v>
+      </c>
     </row>
     <row r="8" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
@@ -4690,27 +4760,27 @@
       </c>
       <c r="N8" s="8">
         <f t="shared" si="0"/>
-        <v>297998.90909090912</v>
+        <v>304243.41666666669</v>
       </c>
       <c r="O8" s="8">
         <f t="shared" si="1"/>
-        <v>43685.818181818184</v>
+        <v>43806.833333333336</v>
       </c>
       <c r="P8" s="8">
         <f t="shared" si="2"/>
-        <v>623</v>
+        <v>697</v>
       </c>
       <c r="Q8" s="9">
         <f t="shared" si="3"/>
-        <v>15784.853932584268</v>
+        <v>15714.150645624104</v>
       </c>
       <c r="R8" s="9">
         <f t="shared" si="4"/>
-        <v>2314.0160513643659</v>
+        <v>2262.6197991391682</v>
       </c>
       <c r="S8" s="10">
         <f t="shared" si="5"/>
-        <v>5.176728933130601</v>
+        <v>5.142106530838654</v>
       </c>
       <c r="T8" s="11">
         <v>330482</v>
@@ -4910,10 +4980,24 @@
       <c r="CG8" s="13">
         <v>5.0655899886639073</v>
       </c>
-      <c r="CJ8" s="11"/>
-      <c r="CK8" s="12"/>
-      <c r="CL8" s="12"/>
-      <c r="CM8" s="13"/>
+      <c r="CH8" s="11">
+        <v>372933</v>
+      </c>
+      <c r="CI8" s="11">
+        <v>45138</v>
+      </c>
+      <c r="CJ8" s="11">
+        <v>74</v>
+      </c>
+      <c r="CK8" s="12">
+        <v>15118.9054054054</v>
+      </c>
+      <c r="CL8" s="12">
+        <v>1829.918918918919</v>
+      </c>
+      <c r="CM8" s="13">
+        <v>4.7612601056272306</v>
+      </c>
     </row>
     <row r="9" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
@@ -4957,27 +5041,27 @@
       </c>
       <c r="N9" s="8">
         <f t="shared" si="0"/>
-        <v>256586.27272727274</v>
+        <v>264443.25</v>
       </c>
       <c r="O9" s="8">
         <f t="shared" si="1"/>
-        <v>8005.636363636364</v>
+        <v>8307</v>
       </c>
       <c r="P9" s="8">
         <f t="shared" si="2"/>
-        <v>474</v>
+        <v>530</v>
       </c>
       <c r="Q9" s="9">
         <f t="shared" si="3"/>
-        <v>17863.601265822785</v>
+        <v>17962.183018867923</v>
       </c>
       <c r="R9" s="9">
         <f t="shared" si="4"/>
-        <v>557.35443037974687</v>
+        <v>564.24905660377362</v>
       </c>
       <c r="S9" s="10">
         <f t="shared" si="5"/>
-        <v>2.3961930435511216</v>
+        <v>2.4058100839410765</v>
       </c>
       <c r="T9" s="11">
         <v>198498</v>
@@ -5177,10 +5261,24 @@
       <c r="CG9" s="13">
         <v>2.3928783055131668</v>
       </c>
-      <c r="CJ9" s="11"/>
-      <c r="CK9" s="12"/>
-      <c r="CL9" s="12"/>
-      <c r="CM9" s="13"/>
+      <c r="CH9" s="11">
+        <v>350870</v>
+      </c>
+      <c r="CI9" s="11">
+        <v>11622</v>
+      </c>
+      <c r="CJ9" s="11">
+        <v>56</v>
+      </c>
+      <c r="CK9" s="12">
+        <v>18796.607142857141</v>
+      </c>
+      <c r="CL9" s="12">
+        <v>622.60714285714289</v>
+      </c>
+      <c r="CM9" s="13">
+        <v>2.511597528230578</v>
+      </c>
     </row>
     <row r="10" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
@@ -5224,27 +5322,27 @@
       </c>
       <c r="N10" s="8">
         <f t="shared" si="0"/>
-        <v>325528.90909090912</v>
+        <v>328066.66666666669</v>
       </c>
       <c r="O10" s="8">
         <f t="shared" si="1"/>
-        <v>11532.90909090909</v>
+        <v>11616.5</v>
       </c>
       <c r="P10" s="8">
         <f t="shared" si="2"/>
-        <v>600</v>
+        <v>663</v>
       </c>
       <c r="Q10" s="9">
         <f t="shared" si="3"/>
-        <v>17904.09</v>
+        <v>17813.574660633483</v>
       </c>
       <c r="R10" s="9">
         <f t="shared" si="4"/>
-        <v>634.30999999999995</v>
+        <v>630.76018099547514</v>
       </c>
       <c r="S10" s="10">
         <f t="shared" si="5"/>
-        <v>2.6568124157883841</v>
+        <v>2.6557615234685255</v>
       </c>
       <c r="T10" s="11">
         <v>324944</v>
@@ -5444,10 +5542,24 @@
       <c r="CG10" s="13">
         <v>2.7122099794700918</v>
       </c>
-      <c r="CJ10" s="11"/>
-      <c r="CK10" s="12"/>
-      <c r="CL10" s="12"/>
-      <c r="CM10" s="13"/>
+      <c r="CH10" s="11">
+        <v>355982</v>
+      </c>
+      <c r="CI10" s="11">
+        <v>12536</v>
+      </c>
+      <c r="CJ10" s="11">
+        <v>63</v>
+      </c>
+      <c r="CK10" s="12">
+        <v>16951.523809523809</v>
+      </c>
+      <c r="CL10" s="12">
+        <v>596.95238095238096</v>
+      </c>
+      <c r="CM10" s="13">
+        <v>2.644201707950081</v>
+      </c>
     </row>
     <row r="11" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
@@ -5491,27 +5603,27 @@
       </c>
       <c r="N11" s="8">
         <f t="shared" si="0"/>
-        <v>342481.63636363635</v>
+        <v>343006.25</v>
       </c>
       <c r="O11" s="8">
         <f t="shared" si="1"/>
-        <v>13013.90909090909</v>
+        <v>12948.166666666666</v>
       </c>
       <c r="P11" s="8">
         <f t="shared" si="2"/>
-        <v>613</v>
+        <v>671</v>
       </c>
       <c r="Q11" s="9">
         <f t="shared" si="3"/>
-        <v>18437.021207177815</v>
+        <v>18402.719821162445</v>
       </c>
       <c r="R11" s="9">
         <f t="shared" si="4"/>
-        <v>700.58564437194127</v>
+        <v>694.68554396423247</v>
       </c>
       <c r="S11" s="10">
         <f t="shared" si="5"/>
-        <v>2.7514589075598077</v>
+        <v>2.7423642514501751</v>
       </c>
       <c r="T11" s="11">
         <v>297191</v>
@@ -5711,10 +5823,24 @@
       <c r="CG11" s="13">
         <v>2.9988755207244471</v>
       </c>
-      <c r="CJ11" s="11"/>
-      <c r="CK11" s="12"/>
-      <c r="CL11" s="12"/>
-      <c r="CM11" s="13"/>
+      <c r="CH11" s="11">
+        <v>348777</v>
+      </c>
+      <c r="CI11" s="11">
+        <v>12225</v>
+      </c>
+      <c r="CJ11" s="11">
+        <v>58</v>
+      </c>
+      <c r="CK11" s="12">
+        <v>18040.189655172409</v>
+      </c>
+      <c r="CL11" s="12">
+        <v>632.32758620689651</v>
+      </c>
+      <c r="CM11" s="13">
+        <v>2.642323034244221</v>
+      </c>
     </row>
     <row r="12" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
@@ -5758,27 +5884,27 @@
       </c>
       <c r="N12" s="8">
         <f t="shared" si="0"/>
-        <v>221979.18181818182</v>
+        <v>225252.58333333334</v>
       </c>
       <c r="O12" s="8">
         <f t="shared" si="1"/>
-        <v>14823</v>
+        <v>15326</v>
       </c>
       <c r="P12" s="8">
         <f t="shared" si="2"/>
-        <v>467</v>
+        <v>522</v>
       </c>
       <c r="Q12" s="9">
         <f t="shared" si="3"/>
-        <v>15685.895074946468</v>
+        <v>15534.660919540231</v>
       </c>
       <c r="R12" s="9">
         <f t="shared" si="4"/>
-        <v>1047.4496788008564</v>
+        <v>1056.9655172413793</v>
       </c>
       <c r="S12" s="10">
         <f t="shared" si="5"/>
-        <v>3.4965278523766257</v>
+        <v>3.529378836315662</v>
       </c>
       <c r="T12" s="11">
         <v>187436</v>
@@ -5978,10 +6104,24 @@
       <c r="CG12" s="13">
         <v>4.2839923207818904</v>
       </c>
-      <c r="CJ12" s="11"/>
-      <c r="CK12" s="12"/>
-      <c r="CL12" s="12"/>
-      <c r="CM12" s="13"/>
+      <c r="CH12" s="11">
+        <v>261260</v>
+      </c>
+      <c r="CI12" s="11">
+        <v>20859</v>
+      </c>
+      <c r="CJ12" s="11">
+        <v>55</v>
+      </c>
+      <c r="CK12" s="12">
+        <v>14250.54545454545</v>
+      </c>
+      <c r="CL12" s="12">
+        <v>1137.7636363636359</v>
+      </c>
+      <c r="CM12" s="13">
+        <v>3.8907396596450612</v>
+      </c>
     </row>
     <row r="13" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
@@ -6160,27 +6300,27 @@
       </c>
       <c r="N14" s="8">
         <f t="shared" si="0"/>
-        <v>281024.72727272729</v>
+        <v>279501.91666666669</v>
       </c>
       <c r="O14" s="8">
         <f t="shared" si="1"/>
-        <v>11334.818181818182</v>
+        <v>11279.25</v>
       </c>
       <c r="P14" s="8">
         <f t="shared" si="2"/>
-        <v>585</v>
+        <v>637</v>
       </c>
       <c r="Q14" s="9">
         <f t="shared" si="3"/>
-        <v>15852.676923076924</v>
+        <v>15796.026687598116</v>
       </c>
       <c r="R14" s="9">
         <f t="shared" si="4"/>
-        <v>639.4</v>
+        <v>637.44583987441126</v>
       </c>
       <c r="S14" s="10">
         <f t="shared" si="5"/>
-        <v>2.7767696231820471</v>
+        <v>2.7788680647835071</v>
       </c>
       <c r="T14" s="11">
         <v>305464</v>
@@ -6380,10 +6520,24 @@
       <c r="CG14" s="13">
         <v>2.4877541345721741</v>
       </c>
-      <c r="CJ14" s="11"/>
-      <c r="CK14" s="12"/>
-      <c r="CL14" s="12"/>
-      <c r="CM14" s="13"/>
+      <c r="CH14" s="11">
+        <v>262751</v>
+      </c>
+      <c r="CI14" s="11">
+        <v>10668</v>
+      </c>
+      <c r="CJ14" s="11">
+        <v>52</v>
+      </c>
+      <c r="CK14" s="12">
+        <v>15158.711538461541</v>
+      </c>
+      <c r="CL14" s="12">
+        <v>615.46153846153845</v>
+      </c>
+      <c r="CM14" s="13">
+        <v>2.801950922399568</v>
+      </c>
     </row>
     <row r="15" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
@@ -6560,27 +6714,27 @@
       </c>
       <c r="N16" s="8">
         <f t="shared" si="0"/>
-        <v>330749.84727272729</v>
+        <v>328260.02666666667</v>
       </c>
       <c r="O16" s="8">
         <f t="shared" si="1"/>
-        <v>164662.45454545456</v>
+        <v>166813.75</v>
       </c>
       <c r="P16" s="8">
         <f t="shared" si="2"/>
-        <v>707</v>
+        <v>767</v>
       </c>
       <c r="Q16" s="9">
         <f t="shared" si="3"/>
-        <v>15438.111683168318</v>
+        <v>15407.250273794005</v>
       </c>
       <c r="R16" s="9">
         <f t="shared" si="4"/>
-        <v>7685.8005657708627</v>
+        <v>7829.5893089960891</v>
       </c>
       <c r="S16" s="10">
         <f t="shared" si="5"/>
-        <v>9.6422799601591738</v>
+        <v>9.7373179341718696</v>
       </c>
       <c r="T16" s="11">
         <v>406091.32</v>
@@ -6780,10 +6934,24 @@
       <c r="CG16" s="13">
         <v>9.4631944941898212</v>
       </c>
-      <c r="CJ16" s="11"/>
-      <c r="CK16" s="12"/>
-      <c r="CL16" s="12"/>
-      <c r="CM16" s="13"/>
+      <c r="CH16" s="11">
+        <v>300872</v>
+      </c>
+      <c r="CI16" s="11">
+        <v>190478</v>
+      </c>
+      <c r="CJ16" s="11">
+        <v>60</v>
+      </c>
+      <c r="CK16" s="12">
+        <v>15043.6</v>
+      </c>
+      <c r="CL16" s="12">
+        <v>9523.9</v>
+      </c>
+      <c r="CM16" s="13">
+        <v>10.78273564831153</v>
+      </c>
     </row>
     <row r="17" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
@@ -6960,27 +7128,27 @@
       </c>
       <c r="N18" s="8">
         <f t="shared" si="0"/>
-        <v>165016.63636363635</v>
+        <v>166520.33333333334</v>
       </c>
       <c r="O18" s="8">
         <f t="shared" si="1"/>
-        <v>73840.818181818177</v>
+        <v>75045.75</v>
       </c>
       <c r="P18" s="8">
         <f t="shared" si="2"/>
-        <v>631</v>
+        <v>693</v>
       </c>
       <c r="Q18" s="9">
         <f t="shared" si="3"/>
-        <v>8630.0301109350239</v>
+        <v>8650.4069264069258</v>
       </c>
       <c r="R18" s="9">
         <f t="shared" si="4"/>
-        <v>3861.7226624405703</v>
+        <v>3898.4805194805194</v>
       </c>
       <c r="S18" s="10">
         <f t="shared" si="5"/>
-        <v>10.607078095006399</v>
+        <v>10.635987459576233</v>
       </c>
       <c r="T18" s="11">
         <v>187236</v>
@@ -7180,10 +7348,24 @@
       <c r="CG18" s="13">
         <v>11.20864030745226</v>
       </c>
-      <c r="CJ18" s="11"/>
-      <c r="CK18" s="12"/>
-      <c r="CL18" s="12"/>
-      <c r="CM18" s="13"/>
+      <c r="CH18" s="11">
+        <v>183061</v>
+      </c>
+      <c r="CI18" s="11">
+        <v>88300</v>
+      </c>
+      <c r="CJ18" s="11">
+        <v>62</v>
+      </c>
+      <c r="CK18" s="12">
+        <v>8857.790322580644</v>
+      </c>
+      <c r="CL18" s="12">
+        <v>4272.5806451612907</v>
+      </c>
+      <c r="CM18" s="13">
+        <v>10.953990469844429</v>
+      </c>
     </row>
     <row r="19" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
@@ -7227,27 +7409,27 @@
       </c>
       <c r="N19" s="8">
         <f t="shared" si="0"/>
-        <v>86706.777777777781</v>
+        <v>90730.7</v>
       </c>
       <c r="O19" s="8">
         <f t="shared" si="1"/>
-        <v>142799.11111111112</v>
+        <v>149908.70000000001</v>
       </c>
       <c r="P19" s="8">
         <f t="shared" si="2"/>
-        <v>402</v>
+        <v>467</v>
       </c>
       <c r="Q19" s="9">
         <f t="shared" si="3"/>
-        <v>5823.5895522388055</v>
+        <v>5828.5246252676661</v>
       </c>
       <c r="R19" s="9">
         <f t="shared" si="4"/>
-        <v>9590.9850746268658</v>
+        <v>9630.1092077087796</v>
       </c>
       <c r="S19" s="10">
         <f t="shared" si="5"/>
-        <v>20.785730804993317</v>
+        <v>20.768650610992641</v>
       </c>
       <c r="T19" s="11">
         <v>29248</v>
@@ -7423,10 +7605,24 @@
       <c r="CG19" s="13">
         <v>20.717365902118111</v>
       </c>
-      <c r="CJ19" s="11"/>
-      <c r="CK19" s="12"/>
-      <c r="CL19" s="12"/>
-      <c r="CM19" s="13"/>
+      <c r="CH19" s="11">
+        <v>126946</v>
+      </c>
+      <c r="CI19" s="11">
+        <v>213895</v>
+      </c>
+      <c r="CJ19" s="11">
+        <v>65</v>
+      </c>
+      <c r="CK19" s="12">
+        <v>5859.0461538461541</v>
+      </c>
+      <c r="CL19" s="12">
+        <v>9872.076923076922</v>
+      </c>
+      <c r="CM19" s="13">
+        <v>20.614928864986549</v>
+      </c>
     </row>
     <row r="20" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
@@ -7470,27 +7666,27 @@
       </c>
       <c r="N20" s="8">
         <f t="shared" si="0"/>
-        <v>321798.09090909088</v>
+        <v>327981.75</v>
       </c>
       <c r="O20" s="8">
         <f t="shared" si="1"/>
-        <v>4911</v>
+        <v>5058.25</v>
       </c>
       <c r="P20" s="8">
         <f t="shared" si="2"/>
-        <v>610</v>
+        <v>673</v>
       </c>
       <c r="Q20" s="9">
         <f t="shared" si="3"/>
-        <v>17408.749180327868</v>
+        <v>17544.343239227339</v>
       </c>
       <c r="R20" s="9">
         <f t="shared" si="4"/>
-        <v>265.67704918032786</v>
+        <v>270.57503714710253</v>
       </c>
       <c r="S20" s="10">
         <f t="shared" si="5"/>
-        <v>1.7238989158058913</v>
+        <v>1.73296204619908</v>
       </c>
       <c r="T20" s="11">
         <v>370489</v>
@@ -7690,10 +7886,24 @@
       <c r="CG20" s="13">
         <v>1.7743639573344721</v>
       </c>
-      <c r="CJ20" s="11"/>
-      <c r="CK20" s="12"/>
-      <c r="CL20" s="12"/>
-      <c r="CM20" s="13"/>
+      <c r="CH20" s="11">
+        <v>396002</v>
+      </c>
+      <c r="CI20" s="11">
+        <v>6678</v>
+      </c>
+      <c r="CJ20" s="11">
+        <v>63</v>
+      </c>
+      <c r="CK20" s="12">
+        <v>18857.238095238099</v>
+      </c>
+      <c r="CL20" s="12">
+        <v>318</v>
+      </c>
+      <c r="CM20" s="13">
+        <v>1.8326564805241581</v>
+      </c>
     </row>
     <row r="21" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
@@ -8005,27 +8215,27 @@
       </c>
       <c r="N23" s="8">
         <f t="shared" si="0"/>
-        <v>197372.36363636365</v>
+        <v>210719.16666666666</v>
       </c>
       <c r="O23" s="8">
         <f t="shared" si="1"/>
-        <v>5891</v>
+        <v>6311.583333333333</v>
       </c>
       <c r="P23" s="8">
         <f t="shared" si="2"/>
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="Q23" s="9">
         <f t="shared" si="3"/>
-        <v>17276.625994694958</v>
+        <v>17641.60465116279</v>
       </c>
       <c r="R23" s="9">
         <f t="shared" si="4"/>
-        <v>515.65782493368704</v>
+        <v>528.41162790697672</v>
       </c>
       <c r="S23" s="10">
         <f t="shared" si="5"/>
-        <v>2.4707971516389686</v>
+        <v>2.4666902944878553</v>
       </c>
       <c r="T23" s="11">
         <v>209199</v>
@@ -8225,10 +8435,24 @@
       <c r="CG23" s="13">
         <v>2.431422495122221</v>
       </c>
-      <c r="CJ23" s="11"/>
-      <c r="CK23" s="12"/>
-      <c r="CL23" s="12"/>
-      <c r="CM23" s="13"/>
+      <c r="CH23" s="11">
+        <v>357534</v>
+      </c>
+      <c r="CI23" s="11">
+        <v>10938</v>
+      </c>
+      <c r="CJ23" s="11">
+        <v>53</v>
+      </c>
+      <c r="CK23" s="12">
+        <v>20237.773584905659</v>
+      </c>
+      <c r="CL23" s="12">
+        <v>619.13207547169804</v>
+      </c>
+      <c r="CM23" s="13">
+        <v>2.42151486582561</v>
+      </c>
     </row>
     <row r="24" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
@@ -8272,27 +8496,27 @@
       </c>
       <c r="N24" s="8">
         <f t="shared" si="0"/>
-        <v>89484.909090909088</v>
+        <v>89597.583333333328</v>
       </c>
       <c r="O24" s="8">
         <f t="shared" si="1"/>
-        <v>260585.72727272726</v>
+        <v>260399.91666666666</v>
       </c>
       <c r="P24" s="8">
         <f t="shared" si="2"/>
-        <v>597</v>
+        <v>653</v>
       </c>
       <c r="Q24" s="9">
         <f t="shared" si="3"/>
-        <v>4946.4020100502512</v>
+        <v>4939.5298621745787</v>
       </c>
       <c r="R24" s="9">
         <f t="shared" si="4"/>
-        <v>14404.236180904521</v>
+        <v>14355.891271056662</v>
       </c>
       <c r="S24" s="10">
         <f t="shared" si="5"/>
-        <v>26.68060141556008</v>
+        <v>26.643567249805582</v>
       </c>
       <c r="T24" s="11">
         <v>77550</v>
@@ -8492,10 +8716,24 @@
       <c r="CG24" s="13">
         <v>28.53981719664932</v>
       </c>
-      <c r="CJ24" s="11"/>
-      <c r="CK24" s="12"/>
-      <c r="CL24" s="12"/>
-      <c r="CM24" s="13"/>
+      <c r="CH24" s="11">
+        <v>90837</v>
+      </c>
+      <c r="CI24" s="11">
+        <v>258356</v>
+      </c>
+      <c r="CJ24" s="11">
+        <v>56</v>
+      </c>
+      <c r="CK24" s="12">
+        <v>4866.2678571428569</v>
+      </c>
+      <c r="CL24" s="12">
+        <v>13840.5</v>
+      </c>
+      <c r="CM24" s="13">
+        <v>26.236191426506071</v>
+      </c>
     </row>
     <row r="25" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
@@ -8539,27 +8777,27 @@
       </c>
       <c r="N25" s="8">
         <f t="shared" si="0"/>
-        <v>177796.18181818182</v>
+        <v>178377.08333333334</v>
       </c>
       <c r="O25" s="8">
         <f t="shared" si="1"/>
-        <v>34273</v>
+        <v>33934.583333333336</v>
       </c>
       <c r="P25" s="8">
         <f t="shared" si="2"/>
-        <v>523</v>
+        <v>571</v>
       </c>
       <c r="Q25" s="9">
         <f t="shared" si="3"/>
-        <v>11218.497131931166</v>
+        <v>11246.190893169878</v>
       </c>
       <c r="R25" s="9">
         <f t="shared" si="4"/>
-        <v>2162.5411089866157</v>
+        <v>2139.4833625218916</v>
       </c>
       <c r="S25" s="10">
         <f t="shared" si="5"/>
-        <v>6.8076981001431713</v>
+        <v>6.7733208919186554</v>
       </c>
       <c r="T25" s="11">
         <v>164013</v>
@@ -8759,10 +8997,24 @@
       <c r="CG25" s="13">
         <v>5.849633264148304</v>
       </c>
-      <c r="CJ25" s="11"/>
-      <c r="CK25" s="12"/>
-      <c r="CL25" s="12"/>
-      <c r="CM25" s="13"/>
+      <c r="CH25" s="11">
+        <v>184767</v>
+      </c>
+      <c r="CI25" s="11">
+        <v>30212</v>
+      </c>
+      <c r="CJ25" s="11">
+        <v>48</v>
+      </c>
+      <c r="CK25" s="12">
+        <v>11547.9375</v>
+      </c>
+      <c r="CL25" s="12">
+        <v>1888.25</v>
+      </c>
+      <c r="CM25" s="13">
+        <v>6.3951716014489719</v>
+      </c>
     </row>
     <row r="26" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
@@ -8806,27 +9058,27 @@
       </c>
       <c r="N26" s="8">
         <f t="shared" si="0"/>
-        <v>562110.90909090906</v>
+        <v>557938</v>
       </c>
       <c r="O26" s="8">
         <f t="shared" si="1"/>
-        <v>156224.54545454544</v>
+        <v>157019.58333333334</v>
       </c>
       <c r="P26" s="8">
         <f t="shared" si="2"/>
-        <v>801</v>
+        <v>875</v>
       </c>
       <c r="Q26" s="9">
         <f t="shared" si="3"/>
-        <v>23158.127340823972</v>
+        <v>22955.163428571428</v>
       </c>
       <c r="R26" s="9">
         <f t="shared" si="4"/>
-        <v>6436.2172284644203</v>
+        <v>6460.2342857142858</v>
       </c>
       <c r="S26" s="10">
         <f t="shared" si="5"/>
-        <v>7.1310672173662306</v>
+        <v>7.1782876853879189</v>
       </c>
       <c r="T26" s="11">
         <v>551602</v>
@@ -9026,10 +9278,24 @@
       <c r="CG26" s="13">
         <v>7.2793465676469236</v>
       </c>
-      <c r="CJ26" s="11"/>
-      <c r="CK26" s="12"/>
-      <c r="CL26" s="12"/>
-      <c r="CM26" s="13"/>
+      <c r="CH26" s="11">
+        <v>512036</v>
+      </c>
+      <c r="CI26" s="11">
+        <v>165765</v>
+      </c>
+      <c r="CJ26" s="11">
+        <v>74</v>
+      </c>
+      <c r="CK26" s="12">
+        <v>20758.216216216209</v>
+      </c>
+      <c r="CL26" s="12">
+        <v>6720.2027027027016</v>
+      </c>
+      <c r="CM26" s="13">
+        <v>7.6977128336264897</v>
+      </c>
     </row>
     <row r="27" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
@@ -9073,27 +9339,27 @@
       </c>
       <c r="N27" s="8">
         <f t="shared" si="0"/>
-        <v>462752.27272727271</v>
+        <v>460689.66666666669</v>
       </c>
       <c r="O27" s="8">
         <f t="shared" si="1"/>
-        <v>115137.72727272728</v>
+        <v>114796.16666666667</v>
       </c>
       <c r="P27" s="8">
         <f t="shared" si="2"/>
-        <v>759</v>
+        <v>820</v>
       </c>
       <c r="Q27" s="9">
         <f t="shared" si="3"/>
-        <v>20119.664031620552</v>
+        <v>20225.400000000001</v>
       </c>
       <c r="R27" s="9">
         <f t="shared" si="4"/>
-        <v>5005.98814229249</v>
+        <v>5039.8317073170729</v>
       </c>
       <c r="S27" s="10">
         <f t="shared" si="5"/>
-        <v>6.6967144334503015</v>
+        <v>6.7035682798563121</v>
       </c>
       <c r="T27" s="11">
         <v>427151</v>
@@ -9293,10 +9559,24 @@
       <c r="CG27" s="13">
         <v>6.7404494622788551</v>
       </c>
-      <c r="CJ27" s="11"/>
-      <c r="CK27" s="12"/>
-      <c r="CL27" s="12"/>
-      <c r="CM27" s="13"/>
+      <c r="CH27" s="11">
+        <v>438001</v>
+      </c>
+      <c r="CI27" s="11">
+        <v>111039</v>
+      </c>
+      <c r="CJ27" s="11">
+        <v>61</v>
+      </c>
+      <c r="CK27" s="12">
+        <v>21541.03278688524</v>
+      </c>
+      <c r="CL27" s="12">
+        <v>5460.9344262295081</v>
+      </c>
+      <c r="CM27" s="13">
+        <v>6.7789605903224253</v>
+      </c>
     </row>
     <row r="28" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
@@ -9602,27 +9882,27 @@
       </c>
       <c r="N30" s="8">
         <f t="shared" si="0"/>
-        <v>261213.27272727274</v>
+        <v>265161.33333333331</v>
       </c>
       <c r="O30" s="8">
         <f t="shared" si="1"/>
-        <v>9609.363636363636</v>
+        <v>9762.25</v>
       </c>
       <c r="P30" s="8">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>464</v>
       </c>
       <c r="Q30" s="9">
         <f t="shared" si="3"/>
-        <v>20523.900000000001</v>
+        <v>20572.862068965514</v>
       </c>
       <c r="R30" s="9">
         <f t="shared" si="4"/>
-        <v>755.0214285714286</v>
+        <v>757.41594827586209</v>
       </c>
       <c r="S30" s="10">
         <f t="shared" si="5"/>
-        <v>2.6359717553247508</v>
+        <v>2.637140775714355</v>
       </c>
       <c r="T30" s="11">
         <v>244240</v>
@@ -9822,10 +10102,24 @@
       <c r="CG30" s="13">
         <v>2.65</v>
       </c>
-      <c r="CJ30" s="11"/>
-      <c r="CK30" s="12"/>
-      <c r="CL30" s="12"/>
-      <c r="CM30" s="13"/>
+      <c r="CH30" s="11">
+        <v>308590</v>
+      </c>
+      <c r="CI30" s="11">
+        <v>11444</v>
+      </c>
+      <c r="CJ30" s="11">
+        <v>44</v>
+      </c>
+      <c r="CK30" s="12">
+        <v>21040.227272727268</v>
+      </c>
+      <c r="CL30" s="12">
+        <v>780.27272727272725</v>
+      </c>
+      <c r="CM30" s="13">
+        <v>2.65</v>
+      </c>
     </row>
     <row r="31" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
@@ -10002,27 +10296,27 @@
       </c>
       <c r="N32" s="8">
         <f t="shared" si="0"/>
-        <v>222646.18181818182</v>
+        <v>229515.58333333334</v>
       </c>
       <c r="O32" s="8">
         <f t="shared" si="1"/>
-        <v>3940.2727272727275</v>
+        <v>4012.5</v>
       </c>
       <c r="P32" s="8">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>462</v>
       </c>
       <c r="Q32" s="9">
         <f t="shared" si="3"/>
-        <v>17493.62857142857</v>
+        <v>17884.331168831166</v>
       </c>
       <c r="R32" s="9">
         <f t="shared" si="4"/>
-        <v>309.59285714285716</v>
+        <v>312.66233766233768</v>
       </c>
       <c r="S32" s="10">
         <f t="shared" si="5"/>
-        <v>1.9006605013195701</v>
+        <v>1.8896190533059105</v>
       </c>
       <c r="T32" s="11">
         <v>117841</v>
@@ -10222,10 +10516,24 @@
       <c r="CG32" s="13">
         <v>1.728368888342328</v>
       </c>
-      <c r="CJ32" s="11"/>
-      <c r="CK32" s="12"/>
-      <c r="CL32" s="12"/>
-      <c r="CM32" s="13"/>
+      <c r="CH32" s="11">
+        <v>305079</v>
+      </c>
+      <c r="CI32" s="11">
+        <v>4807</v>
+      </c>
+      <c r="CJ32" s="11">
+        <v>42</v>
+      </c>
+      <c r="CK32" s="12">
+        <v>21791.357142857141</v>
+      </c>
+      <c r="CL32" s="12">
+        <v>343.35714285714278</v>
+      </c>
+      <c r="CM32" s="13">
+        <v>1.7681631251556551</v>
+      </c>
     </row>
     <row r="33" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
@@ -10269,27 +10577,27 @@
       </c>
       <c r="N33" s="8">
         <f t="shared" si="0"/>
-        <v>263592</v>
+        <v>272703.75</v>
       </c>
       <c r="O33" s="8">
         <f t="shared" si="1"/>
-        <v>21585.363636363636</v>
+        <v>22242.416666666668</v>
       </c>
       <c r="P33" s="8">
         <f t="shared" si="2"/>
-        <v>630</v>
+        <v>695</v>
       </c>
       <c r="Q33" s="9">
         <f t="shared" si="3"/>
-        <v>13807.199999999999</v>
+        <v>14125.661870503596</v>
       </c>
       <c r="R33" s="9">
         <f t="shared" si="4"/>
-        <v>1130.6619047619047</v>
+        <v>1152.125179856115</v>
       </c>
       <c r="S33" s="10">
         <f t="shared" si="5"/>
-        <v>4.0603194285579898</v>
+        <v>4.0527829403032722</v>
       </c>
       <c r="T33" s="11">
         <v>291624</v>
@@ -10489,10 +10797,24 @@
       <c r="CG33" s="13">
         <v>4.0727749204517423</v>
       </c>
-      <c r="CJ33" s="11"/>
-      <c r="CK33" s="12"/>
-      <c r="CL33" s="12"/>
-      <c r="CM33" s="13"/>
+      <c r="CH33" s="11">
+        <v>372933</v>
+      </c>
+      <c r="CI33" s="11">
+        <v>29470</v>
+      </c>
+      <c r="CJ33" s="11">
+        <v>65</v>
+      </c>
+      <c r="CK33" s="12">
+        <v>17212.292307692311</v>
+      </c>
+      <c r="CL33" s="12">
+        <v>1360.153846153846</v>
+      </c>
+      <c r="CM33" s="13">
+        <v>3.9698815695013758</v>
+      </c>
     </row>
     <row r="34" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
@@ -10671,27 +10993,27 @@
       </c>
       <c r="N35" s="8">
         <f t="shared" ref="N35:N62" si="6">IFERROR(AVERAGE(T35,Z35,AF35,AL35,AR35,AX35,BD35,BJ35,BP35,BV35,CB35,CH35)," ")</f>
-        <v>290123.72727272729</v>
+        <v>303057.41666666669</v>
       </c>
       <c r="O35" s="8">
         <f t="shared" ref="O35:O62" si="7">IFERROR(AVERAGE(U35,AA35,AG35,AM35,AS35,AY35,BE35,BK35,BQ35,BW35,CC35,CI35)," ")</f>
-        <v>26333.363636363636</v>
+        <v>26961.083333333332</v>
       </c>
       <c r="P35" s="8">
         <f t="shared" ref="P35:P62" si="8">IFERROR(SUM(V35,AB35,AH35,AN35,AT35,AZ35,BF35,BL35,BR35,BX35,CD35,CJ35)," ")</f>
-        <v>684</v>
+        <v>753</v>
       </c>
       <c r="Q35" s="9">
         <f t="shared" ref="Q35:Q62" si="9">IFERROR(SUM(T35,Z35,AF35,AL35,AR35,AX35,BD35,BJ35,BP35,BV35,CB35,CH35)/P35*3," ")</f>
-        <v>13997.197368421053</v>
+        <v>14488.800796812748</v>
       </c>
       <c r="R35" s="9">
         <f t="shared" ref="R35:R62" si="10">IFERROR(SUM(U35,AA35,AG35,AM35,AS35,AY35,BE35,BK35,BQ35,BW35,CC35,CI35)/P35*3," ")</f>
-        <v>1270.469298245614</v>
+        <v>1288.9760956175298</v>
       </c>
       <c r="S35" s="10">
         <f t="shared" ref="S35:S62" si="11">IFERROR(AVERAGE(Y35,AE35,AK35,AQ35,AW35,BC35,BI35,BO35,BU35,CA35,CG35,CM35)," ")</f>
-        <v>4.2571860240728139</v>
+        <v>4.2268655598484299</v>
       </c>
       <c r="T35" s="11">
         <v>279536</v>
@@ -10891,10 +11213,24 @@
       <c r="CG35" s="13">
         <v>4.0576287065610064</v>
       </c>
-      <c r="CJ35" s="11"/>
-      <c r="CK35" s="12"/>
-      <c r="CL35" s="12"/>
-      <c r="CM35" s="13"/>
+      <c r="CH35" s="11">
+        <v>445328</v>
+      </c>
+      <c r="CI35" s="11">
+        <v>33866</v>
+      </c>
+      <c r="CJ35" s="11">
+        <v>69</v>
+      </c>
+      <c r="CK35" s="12">
+        <v>19362.08695652174</v>
+      </c>
+      <c r="CL35" s="12">
+        <v>1472.434782608696</v>
+      </c>
+      <c r="CM35" s="13">
+        <v>3.8933404533802052</v>
+      </c>
     </row>
     <row r="36" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
@@ -10938,27 +11274,27 @@
       </c>
       <c r="N36" s="8">
         <f t="shared" si="6"/>
-        <v>65258.375</v>
+        <v>61819.444444444445</v>
       </c>
       <c r="O36" s="8">
         <f t="shared" si="7"/>
-        <v>4155.875</v>
+        <v>3967.4444444444443</v>
       </c>
       <c r="P36" s="8">
         <f t="shared" si="8"/>
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="Q36" s="9">
         <f t="shared" si="9"/>
-        <v>17211</v>
+        <v>17031.887755102041</v>
       </c>
       <c r="R36" s="9">
         <f t="shared" si="10"/>
-        <v>1096.0549450549452</v>
+        <v>1093.0714285714284</v>
       </c>
       <c r="S36" s="10">
         <f t="shared" si="11"/>
-        <v>6.2591940637615542</v>
+        <v>5.9838808868177837</v>
       </c>
       <c r="T36" s="11">
         <v>121136</v>
@@ -11122,10 +11458,24 @@
       <c r="CE36" s="12"/>
       <c r="CF36" s="12"/>
       <c r="CG36" s="13"/>
-      <c r="CJ36" s="11"/>
-      <c r="CK36" s="12"/>
-      <c r="CL36" s="12"/>
-      <c r="CM36" s="13"/>
+      <c r="CH36" s="11">
+        <v>34308</v>
+      </c>
+      <c r="CI36" s="11">
+        <v>2460</v>
+      </c>
+      <c r="CJ36" s="11">
+        <v>7</v>
+      </c>
+      <c r="CK36" s="12">
+        <v>14703.428571428571</v>
+      </c>
+      <c r="CL36" s="12">
+        <v>1054.285714285714</v>
+      </c>
+      <c r="CM36" s="13">
+        <v>3.7813754712676229</v>
+      </c>
     </row>
     <row r="37" spans="1:91" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
@@ -11169,27 +11519,27 @@
       </c>
       <c r="N37" s="8">
         <f t="shared" si="6"/>
-        <v>252787.33333333334</v>
+        <v>261351.8</v>
       </c>
       <c r="O37" s="8">
         <f t="shared" si="7"/>
-        <v>71738.222222222219</v>
+        <v>73940</v>
       </c>
       <c r="P37" s="8">
         <f t="shared" si="8"/>
-        <v>523</v>
+        <v>590</v>
       </c>
       <c r="Q37" s="9">
         <f t="shared" si="9"/>
-        <v>13050.206500956025</v>
+        <v>13289.074576271189</v>
       </c>
       <c r="R37" s="9">
         <f t="shared" si="10"/>
-        <v>3703.5028680688338</v>
+        <v>3759.6610169491523</v>
       </c>
       <c r="S37" s="10">
         <f t="shared" si="11"/>
-        <v>6.8446844814643253</v>
+        <v>6.8894869961296461</v>
       </c>
       <c r="T37" s="11">
         <v>300561</v>
@@ -11365,10 +11715,24 @@
       <c r="CG37" s="13">
         <v>7.9627724103633826</v>
       </c>
-      <c r="CJ37" s="11"/>
-      <c r="CK37" s="12"/>
-      <c r="CL37" s="12"/>
-      <c r="CM37" s="13"/>
+      <c r="CH37" s="11">
+        <v>338432</v>
+      </c>
+      <c r="CI37" s="11">
+        <v>93756</v>
+      </c>
+      <c r="CJ37" s="11">
+        <v>67</v>
+      </c>
+      <c r="CK37" s="12">
+        <v>15153.671641791039</v>
+      </c>
+      <c r="CL37" s="12">
+        <v>4198.0298507462676</v>
+      </c>
+      <c r="CM37" s="13">
+        <v>7.2927096281175414</v>
+      </c>
     </row>
     <row r="38" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
@@ -11545,27 +11909,27 @@
       </c>
       <c r="N39" s="8">
         <f t="shared" si="6"/>
-        <v>105132.09090909091</v>
+        <v>114271.58333333333</v>
       </c>
       <c r="O39" s="8">
         <f t="shared" si="7"/>
-        <v>80926.818181818177</v>
+        <v>78634.75</v>
       </c>
       <c r="P39" s="8">
         <f t="shared" si="8"/>
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="Q39" s="9">
         <f t="shared" si="9"/>
-        <v>9034.7890625</v>
+        <v>10132.45566502463</v>
       </c>
       <c r="R39" s="9">
         <f t="shared" si="10"/>
-        <v>6954.6484375</v>
+        <v>6972.5394088669946</v>
       </c>
       <c r="S39" s="10">
         <f t="shared" si="11"/>
-        <v>13.668247404814279</v>
+        <v>13.142932028430662</v>
       </c>
       <c r="T39" s="11">
         <v>83807</v>
@@ -11765,10 +12129,24 @@
       <c r="CG39" s="13">
         <v>13.269367273947619</v>
       </c>
-      <c r="CJ39" s="11"/>
-      <c r="CK39" s="12"/>
-      <c r="CL39" s="12"/>
-      <c r="CM39" s="13"/>
+      <c r="CH39" s="11">
+        <v>214806</v>
+      </c>
+      <c r="CI39" s="11">
+        <v>53422</v>
+      </c>
+      <c r="CJ39" s="11">
+        <v>22</v>
+      </c>
+      <c r="CK39" s="12">
+        <v>29291.727272727268</v>
+      </c>
+      <c r="CL39" s="12">
+        <v>7284.818181818182</v>
+      </c>
+      <c r="CM39" s="13">
+        <v>7.3644628882108734</v>
+      </c>
     </row>
     <row r="40" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
@@ -11812,27 +12190,27 @@
       </c>
       <c r="N40" s="8">
         <f t="shared" si="6"/>
-        <v>136385.81818181818</v>
+        <v>139515.16666666666</v>
       </c>
       <c r="O40" s="8">
         <f t="shared" si="7"/>
-        <v>120850.90909090909</v>
+        <v>124253.75</v>
       </c>
       <c r="P40" s="8">
         <f t="shared" si="8"/>
-        <v>571</v>
+        <v>632</v>
       </c>
       <c r="Q40" s="9">
         <f t="shared" si="9"/>
-        <v>7882.1926444833625</v>
+        <v>7947.066455696202</v>
       </c>
       <c r="R40" s="9">
         <f t="shared" si="10"/>
-        <v>6984.3782837127847</v>
+        <v>7077.7452531645558</v>
       </c>
       <c r="S40" s="10">
         <f t="shared" si="11"/>
-        <v>14.923430174845043</v>
+        <v>14.946041280404785</v>
       </c>
       <c r="T40" s="11">
         <v>142761</v>
@@ -12032,10 +12410,24 @@
       <c r="CG40" s="13">
         <v>15.245423669247989</v>
       </c>
-      <c r="CJ40" s="11"/>
-      <c r="CK40" s="12"/>
-      <c r="CL40" s="12"/>
-      <c r="CM40" s="13"/>
+      <c r="CH40" s="11">
+        <v>173938</v>
+      </c>
+      <c r="CI40" s="11">
+        <v>161685</v>
+      </c>
+      <c r="CJ40" s="11">
+        <v>61</v>
+      </c>
+      <c r="CK40" s="12">
+        <v>8554.3278688524588</v>
+      </c>
+      <c r="CL40" s="12">
+        <v>7951.7213114754104</v>
+      </c>
+      <c r="CM40" s="13">
+        <v>15.19476344156195</v>
+      </c>
     </row>
     <row r="41" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
@@ -12346,27 +12738,27 @@
       </c>
       <c r="N42" s="8">
         <f t="shared" si="6"/>
-        <v>243160.45454545456</v>
+        <v>247480.41666666666</v>
       </c>
       <c r="O42" s="8">
         <f t="shared" si="7"/>
-        <v>85373.636363636368</v>
+        <v>86986.25</v>
       </c>
       <c r="P42" s="8">
         <f t="shared" si="8"/>
-        <v>399</v>
+        <v>449</v>
       </c>
       <c r="Q42" s="9">
         <f t="shared" si="9"/>
-        <v>20111.015037593985</v>
+        <v>19842.527839643655</v>
       </c>
       <c r="R42" s="9">
         <f t="shared" si="10"/>
-        <v>7060.9774436090229</v>
+        <v>6974.3986636971058</v>
       </c>
       <c r="S42" s="10">
         <f t="shared" si="11"/>
-        <v>9.9600089304451291</v>
+        <v>9.9633415195747013</v>
       </c>
       <c r="T42" s="11">
         <v>153600</v>
@@ -12566,10 +12958,24 @@
       <c r="CG42" s="13">
         <v>10</v>
       </c>
-      <c r="CJ42" s="11"/>
-      <c r="CK42" s="12"/>
-      <c r="CL42" s="12"/>
-      <c r="CM42" s="13"/>
+      <c r="CH42" s="11">
+        <v>295000</v>
+      </c>
+      <c r="CI42" s="11">
+        <v>104725</v>
+      </c>
+      <c r="CJ42" s="11">
+        <v>50</v>
+      </c>
+      <c r="CK42" s="12">
+        <v>17700</v>
+      </c>
+      <c r="CL42" s="12">
+        <v>6283.5</v>
+      </c>
+      <c r="CM42" s="13">
+        <v>10</v>
+      </c>
     </row>
     <row r="43" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
@@ -12613,27 +13019,27 @@
       </c>
       <c r="N43" s="8">
         <f t="shared" si="6"/>
-        <v>197144.45454545456</v>
+        <v>183737.75</v>
       </c>
       <c r="O43" s="8">
         <f t="shared" si="7"/>
-        <v>125114.36363636363</v>
+        <v>116683.16666666667</v>
       </c>
       <c r="P43" s="8">
         <f t="shared" si="8"/>
-        <v>557</v>
+        <v>570</v>
       </c>
       <c r="Q43" s="9">
         <f t="shared" si="9"/>
-        <v>11680.012567324955</v>
+        <v>11604.489473684211</v>
       </c>
       <c r="R43" s="9">
         <f t="shared" si="10"/>
-        <v>7412.5206463195691</v>
+        <v>7369.4631578947374</v>
       </c>
       <c r="S43" s="10">
         <f t="shared" si="11"/>
-        <v>10.827586585024976</v>
+        <v>10.846797722330821</v>
       </c>
       <c r="T43" s="11">
         <v>197949</v>
@@ -12833,10 +13239,24 @@
       <c r="CG43" s="13">
         <v>11.37028038676354</v>
       </c>
-      <c r="CJ43" s="11"/>
-      <c r="CK43" s="12"/>
-      <c r="CL43" s="12"/>
-      <c r="CM43" s="13"/>
+      <c r="CH43" s="11">
+        <v>36264</v>
+      </c>
+      <c r="CI43" s="11">
+        <v>23940</v>
+      </c>
+      <c r="CJ43" s="11">
+        <v>13</v>
+      </c>
+      <c r="CK43" s="12">
+        <v>8368.6153846153848</v>
+      </c>
+      <c r="CL43" s="12">
+        <v>5524.6153846153848</v>
+      </c>
+      <c r="CM43" s="13">
+        <v>11.058120232695121</v>
+      </c>
     </row>
     <row r="44" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
@@ -12880,27 +13300,27 @@
       </c>
       <c r="N44" s="8">
         <f t="shared" si="6"/>
-        <v>53318.818181818184</v>
+        <v>52472.083333333336</v>
       </c>
       <c r="O44" s="8">
         <f t="shared" si="7"/>
-        <v>236336.72727272726</v>
+        <v>233184.75</v>
       </c>
       <c r="P44" s="8">
         <f t="shared" si="8"/>
-        <v>435</v>
+        <v>471</v>
       </c>
       <c r="Q44" s="9">
         <f t="shared" si="9"/>
-        <v>4044.875862068965</v>
+        <v>4010.6050955414012</v>
       </c>
       <c r="R44" s="9">
         <f t="shared" si="10"/>
-        <v>17928.993103448276</v>
+        <v>17823.038216560508</v>
       </c>
       <c r="S44" s="10">
         <f t="shared" si="11"/>
-        <v>33.999710628306239</v>
+        <v>33.944290434386716</v>
       </c>
       <c r="T44" s="11">
         <v>53460</v>
@@ -13100,10 +13520,24 @@
       <c r="CG44" s="13">
         <v>33.721087495054753</v>
       </c>
-      <c r="CJ44" s="11"/>
-      <c r="CK44" s="12"/>
-      <c r="CL44" s="12"/>
-      <c r="CM44" s="13"/>
+      <c r="CH44" s="11">
+        <v>43158</v>
+      </c>
+      <c r="CI44" s="11">
+        <v>198513</v>
+      </c>
+      <c r="CJ44" s="11">
+        <v>36</v>
+      </c>
+      <c r="CK44" s="12">
+        <v>3596.5</v>
+      </c>
+      <c r="CL44" s="12">
+        <v>16542.75</v>
+      </c>
+      <c r="CM44" s="13">
+        <v>33.334668301271989</v>
+      </c>
     </row>
     <row r="45" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
@@ -13147,27 +13581,27 @@
       </c>
       <c r="N45" s="8">
         <f t="shared" si="6"/>
-        <v>210119.45454545456</v>
+        <v>207194.5</v>
       </c>
       <c r="O45" s="8">
         <f t="shared" si="7"/>
-        <v>12401.09090909091</v>
+        <v>12166.25</v>
       </c>
       <c r="P45" s="8">
         <f t="shared" si="8"/>
-        <v>529</v>
+        <v>575</v>
       </c>
       <c r="Q45" s="9">
         <f t="shared" si="9"/>
-        <v>13107.640831758035</v>
+        <v>12972.177391304347</v>
       </c>
       <c r="R45" s="9">
         <f t="shared" si="10"/>
-        <v>773.60302457466912</v>
+        <v>761.71304347826094</v>
       </c>
       <c r="S45" s="10">
         <f t="shared" si="11"/>
-        <v>3.395249743516001</v>
+        <v>3.3874445657119399</v>
       </c>
       <c r="T45" s="11">
         <v>323850</v>
@@ -13367,10 +13801,24 @@
       <c r="CG45" s="13">
         <v>3.1600954028077268</v>
       </c>
-      <c r="CJ45" s="11"/>
-      <c r="CK45" s="12"/>
-      <c r="CL45" s="12"/>
-      <c r="CM45" s="13"/>
+      <c r="CH45" s="11">
+        <v>175020</v>
+      </c>
+      <c r="CI45" s="11">
+        <v>9583</v>
+      </c>
+      <c r="CJ45" s="11">
+        <v>46</v>
+      </c>
+      <c r="CK45" s="12">
+        <v>11414.34782608696</v>
+      </c>
+      <c r="CL45" s="12">
+        <v>624.97826086956525</v>
+      </c>
+      <c r="CM45" s="13">
+        <v>3.3015876098672701</v>
+      </c>
     </row>
     <row r="46" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
@@ -13414,27 +13862,27 @@
       </c>
       <c r="N46" s="8">
         <f t="shared" si="6"/>
-        <v>170734.18181818182</v>
+        <v>174111.08333333334</v>
       </c>
       <c r="O46" s="8">
         <f t="shared" si="7"/>
-        <v>9984.363636363636</v>
+        <v>10168.833333333334</v>
       </c>
       <c r="P46" s="8">
         <f t="shared" si="8"/>
-        <v>518</v>
+        <v>560</v>
       </c>
       <c r="Q46" s="9">
         <f t="shared" si="9"/>
-        <v>10876.888030888031</v>
+        <v>11192.855357142857</v>
       </c>
       <c r="R46" s="9">
         <f t="shared" si="10"/>
-        <v>636.06949806949808</v>
+        <v>653.71071428571429</v>
       </c>
       <c r="S46" s="10">
         <f t="shared" si="11"/>
-        <v>3.4084365468005942</v>
+        <v>3.4072625964062322</v>
       </c>
       <c r="T46" s="11">
         <v>251379</v>
@@ -13634,10 +14082,24 @@
       <c r="CG46" s="13">
         <v>3.1305857230480298</v>
       </c>
-      <c r="CJ46" s="11"/>
-      <c r="CK46" s="12"/>
-      <c r="CL46" s="12"/>
-      <c r="CM46" s="13"/>
+      <c r="CH46" s="11">
+        <v>211257</v>
+      </c>
+      <c r="CI46" s="11">
+        <v>12198</v>
+      </c>
+      <c r="CJ46" s="11">
+        <v>42</v>
+      </c>
+      <c r="CK46" s="12">
+        <v>15089.78571428571</v>
+      </c>
+      <c r="CL46" s="12">
+        <v>871.28571428571433</v>
+      </c>
+      <c r="CM46" s="13">
+        <v>3.3943491420682501</v>
+      </c>
     </row>
     <row r="47" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
@@ -13681,27 +14143,27 @@
       </c>
       <c r="N47" s="8">
         <f t="shared" si="6"/>
-        <v>208392</v>
+        <v>207599.08333333334</v>
       </c>
       <c r="O47" s="8">
         <f t="shared" si="7"/>
-        <v>12385.454545454546</v>
+        <v>12262.583333333334</v>
       </c>
       <c r="P47" s="8">
         <f t="shared" si="8"/>
-        <v>525</v>
+        <v>582</v>
       </c>
       <c r="Q47" s="9">
         <f t="shared" si="9"/>
-        <v>13098.925714285715</v>
+        <v>12841.180412371134</v>
       </c>
       <c r="R47" s="9">
         <f t="shared" si="10"/>
-        <v>778.51428571428573</v>
+        <v>758.51030927835052</v>
       </c>
       <c r="S47" s="10">
         <f t="shared" si="11"/>
-        <v>3.3835575975119001</v>
+        <v>3.3769757862728347</v>
       </c>
       <c r="T47" s="11">
         <v>306785</v>
@@ -13901,10 +14363,24 @@
       <c r="CG47" s="13">
         <v>2.8457268530200008</v>
       </c>
-      <c r="CJ47" s="11"/>
-      <c r="CK47" s="12"/>
-      <c r="CL47" s="12"/>
-      <c r="CM47" s="13"/>
+      <c r="CH47" s="11">
+        <v>198877</v>
+      </c>
+      <c r="CI47" s="11">
+        <v>10911</v>
+      </c>
+      <c r="CJ47" s="11">
+        <v>57</v>
+      </c>
+      <c r="CK47" s="12">
+        <v>10467.21052631579</v>
+      </c>
+      <c r="CL47" s="12">
+        <v>574.26315789473688</v>
+      </c>
+      <c r="CM47" s="13">
+        <v>3.3045758626431132</v>
+      </c>
     </row>
     <row r="48" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
@@ -14254,27 +14730,27 @@
       </c>
       <c r="N50" s="8">
         <f t="shared" si="6"/>
-        <v>121920.3</v>
+        <v>121864</v>
       </c>
       <c r="O50" s="8">
         <f t="shared" si="7"/>
-        <v>24106</v>
+        <v>23900.727272727272</v>
       </c>
       <c r="P50" s="8">
         <f t="shared" si="8"/>
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="Q50" s="9">
         <f t="shared" si="9"/>
-        <v>10332.228813559323</v>
+        <v>10129.753148614609</v>
       </c>
       <c r="R50" s="9">
         <f t="shared" si="10"/>
-        <v>2042.8813559322034</v>
+        <v>1986.7103274559195</v>
       </c>
       <c r="S50" s="10">
         <f t="shared" si="11"/>
-        <v>6.9082931604544298</v>
+        <v>6.814213477293432</v>
       </c>
       <c r="T50" s="11">
         <v>42720</v>
@@ -14462,10 +14938,24 @@
       <c r="CG50" s="13">
         <v>5.9676058039146707</v>
       </c>
-      <c r="CJ50" s="11"/>
-      <c r="CK50" s="12"/>
-      <c r="CL50" s="12"/>
-      <c r="CM50" s="13"/>
+      <c r="CH50" s="11">
+        <v>121301</v>
+      </c>
+      <c r="CI50" s="11">
+        <v>21848</v>
+      </c>
+      <c r="CJ50" s="11">
+        <v>43</v>
+      </c>
+      <c r="CK50" s="12">
+        <v>8462.8604651162786</v>
+      </c>
+      <c r="CL50" s="12">
+        <v>1524.279069767442</v>
+      </c>
+      <c r="CM50" s="13">
+        <v>5.873416645683454</v>
+      </c>
     </row>
     <row r="51" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
@@ -14678,27 +15168,27 @@
       </c>
       <c r="N52" s="8">
         <f t="shared" si="6"/>
-        <v>26672.3</v>
+        <v>26974.81818181818</v>
       </c>
       <c r="O52" s="8">
         <f t="shared" si="7"/>
-        <v>39109.699999999997</v>
+        <v>40307.909090909088</v>
       </c>
       <c r="P52" s="8">
         <f t="shared" si="8"/>
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="9">
         <f t="shared" si="9"/>
-        <v>4598.6724137931033</v>
+        <v>4612.2746113989633</v>
       </c>
       <c r="R52" s="9">
         <f t="shared" si="10"/>
-        <v>6743.0517241379312</v>
+        <v>6892.025906735752</v>
       </c>
       <c r="S52" s="10">
         <f t="shared" si="11"/>
-        <v>18.920824475001645</v>
+        <v>18.922343857158804</v>
       </c>
       <c r="T52" s="11">
         <v>28700</v>
@@ -14886,10 +15376,24 @@
       <c r="CG52" s="13">
         <v>19.383105970095979</v>
       </c>
-      <c r="CJ52" s="11"/>
-      <c r="CK52" s="12"/>
-      <c r="CL52" s="12"/>
-      <c r="CM52" s="13"/>
+      <c r="CH52" s="11">
+        <v>30000</v>
+      </c>
+      <c r="CI52" s="11">
+        <v>52290</v>
+      </c>
+      <c r="CJ52" s="11">
+        <v>19</v>
+      </c>
+      <c r="CK52" s="12">
+        <v>4736.8421052631584</v>
+      </c>
+      <c r="CL52" s="12">
+        <v>8256.3157894736833</v>
+      </c>
+      <c r="CM52" s="13">
+        <v>18.93753767873039</v>
+      </c>
     </row>
     <row r="53" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
@@ -14921,27 +15425,27 @@
       </c>
       <c r="N53" s="8">
         <f t="shared" si="6"/>
-        <v>252182.44444444444</v>
+        <v>236720.2</v>
       </c>
       <c r="O53" s="8">
         <f t="shared" si="7"/>
-        <v>8818.1111111111113</v>
+        <v>8298.1</v>
       </c>
       <c r="P53" s="8">
         <f t="shared" si="8"/>
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="Q53" s="9">
         <f t="shared" si="9"/>
-        <v>21547.234177215192</v>
+        <v>21455.003021148037</v>
       </c>
       <c r="R53" s="9">
         <f t="shared" si="10"/>
-        <v>753.44620253164567</v>
+        <v>752.09365558912384</v>
       </c>
       <c r="S53" s="10">
         <f t="shared" si="11"/>
-        <v>2.5230266968695361</v>
+        <v>2.5357240271825825</v>
       </c>
       <c r="T53" s="11"/>
       <c r="U53" s="11"/>
@@ -15117,10 +15621,24 @@
       <c r="CG53" s="13">
         <v>2.067391246541177</v>
       </c>
-      <c r="CJ53" s="11"/>
-      <c r="CK53" s="12"/>
-      <c r="CL53" s="12"/>
-      <c r="CM53" s="13"/>
+      <c r="CH53" s="11">
+        <v>97560</v>
+      </c>
+      <c r="CI53" s="11">
+        <v>3618</v>
+      </c>
+      <c r="CJ53" s="11">
+        <v>15</v>
+      </c>
+      <c r="CK53" s="12">
+        <v>19512</v>
+      </c>
+      <c r="CL53" s="12">
+        <v>723.59999999999991</v>
+      </c>
+      <c r="CM53" s="13">
+        <v>2.65</v>
+      </c>
     </row>
     <row r="54" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
@@ -15152,27 +15670,27 @@
       </c>
       <c r="N54" s="8">
         <f t="shared" si="6"/>
-        <v>225840.55555555556</v>
+        <v>213012.5</v>
       </c>
       <c r="O54" s="8">
         <f t="shared" si="7"/>
-        <v>8374.8888888888887</v>
+        <v>7899.2</v>
       </c>
       <c r="P54" s="8">
         <f t="shared" si="8"/>
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="Q54" s="9">
         <f t="shared" si="9"/>
-        <v>21777.482142857145</v>
+        <v>21735.9693877551</v>
       </c>
       <c r="R54" s="9">
         <f t="shared" si="10"/>
-        <v>807.57857142857142</v>
+        <v>806.0408163265306</v>
       </c>
       <c r="S54" s="10">
         <f t="shared" si="11"/>
-        <v>2.6758922947377686</v>
+        <v>2.6733030652639913</v>
       </c>
       <c r="T54" s="11"/>
       <c r="U54" s="11"/>
@@ -15348,10 +15866,24 @@
       <c r="CG54" s="13">
         <v>2.8067071091613629</v>
       </c>
-      <c r="CJ54" s="11"/>
-      <c r="CK54" s="12"/>
-      <c r="CL54" s="12"/>
-      <c r="CM54" s="13"/>
+      <c r="CH54" s="11">
+        <v>97560</v>
+      </c>
+      <c r="CI54" s="11">
+        <v>3618</v>
+      </c>
+      <c r="CJ54" s="11">
+        <v>14</v>
+      </c>
+      <c r="CK54" s="12">
+        <v>20905.71428571429</v>
+      </c>
+      <c r="CL54" s="12">
+        <v>775.28571428571433</v>
+      </c>
+      <c r="CM54" s="13">
+        <v>2.65</v>
+      </c>
     </row>
     <row r="55" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
@@ -15383,27 +15915,27 @@
       </c>
       <c r="N55" s="8">
         <f t="shared" si="6"/>
-        <v>229355.81818181818</v>
+        <v>235282.58333333334</v>
       </c>
       <c r="O55" s="8">
         <f t="shared" si="7"/>
-        <v>4687.090909090909</v>
+        <v>4874.833333333333</v>
       </c>
       <c r="P55" s="8">
         <f t="shared" si="8"/>
-        <v>458</v>
+        <v>505</v>
       </c>
       <c r="Q55" s="9">
         <f t="shared" si="9"/>
-        <v>16525.637554585155</v>
+        <v>16772.619801980196</v>
       </c>
       <c r="R55" s="9">
         <f t="shared" si="10"/>
-        <v>337.71615720524017</v>
+        <v>347.51287128712875</v>
       </c>
       <c r="S55" s="10">
         <f t="shared" si="11"/>
-        <v>2.0422479294337981</v>
+        <v>2.0508695084901611</v>
       </c>
       <c r="T55" s="11">
         <v>201375</v>
@@ -15603,10 +16135,24 @@
       <c r="CG55" s="13">
         <v>2.081579340786587</v>
       </c>
-      <c r="CJ55" s="11"/>
-      <c r="CK55" s="12"/>
-      <c r="CL55" s="12"/>
-      <c r="CM55" s="13"/>
+      <c r="CH55" s="11">
+        <v>300477</v>
+      </c>
+      <c r="CI55" s="11">
+        <v>6940</v>
+      </c>
+      <c r="CJ55" s="11">
+        <v>47</v>
+      </c>
+      <c r="CK55" s="12">
+        <v>19179.38297872341</v>
+      </c>
+      <c r="CL55" s="12">
+        <v>442.97872340425528</v>
+      </c>
+      <c r="CM55" s="13">
+        <v>2.1457068781101571</v>
+      </c>
     </row>
     <row r="56" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
@@ -15638,27 +16184,27 @@
       </c>
       <c r="N56" s="8">
         <f t="shared" si="6"/>
-        <v>238865.54545454544</v>
+        <v>242818.08333333334</v>
       </c>
       <c r="O56" s="8">
         <f t="shared" si="7"/>
-        <v>4510.909090909091</v>
+        <v>4624.666666666667</v>
       </c>
       <c r="P56" s="8">
         <f t="shared" si="8"/>
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="Q56" s="9">
         <f t="shared" si="9"/>
-        <v>17173.339869281048</v>
+        <v>17344.148809523809</v>
       </c>
       <c r="R56" s="9">
         <f t="shared" si="10"/>
-        <v>324.31372549019608</v>
+        <v>330.33333333333337</v>
       </c>
       <c r="S56" s="10">
         <f t="shared" si="11"/>
-        <v>1.9416890925451895</v>
+        <v>1.9487209867511608</v>
       </c>
       <c r="T56" s="11">
         <v>211721</v>
@@ -15858,10 +16404,24 @@
       <c r="CG56" s="13">
         <v>2.085251823362841</v>
       </c>
-      <c r="CJ56" s="11"/>
-      <c r="CK56" s="12"/>
-      <c r="CL56" s="12"/>
-      <c r="CM56" s="13"/>
+      <c r="CH56" s="11">
+        <v>286296</v>
+      </c>
+      <c r="CI56" s="11">
+        <v>5876</v>
+      </c>
+      <c r="CJ56" s="11">
+        <v>45</v>
+      </c>
+      <c r="CK56" s="12">
+        <v>19086.400000000001</v>
+      </c>
+      <c r="CL56" s="12">
+        <v>391.73333333333329</v>
+      </c>
+      <c r="CM56" s="13">
+        <v>2.0260718230168449</v>
+      </c>
     </row>
     <row r="57" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
@@ -15893,27 +16453,27 @@
       </c>
       <c r="N57" s="8">
         <f t="shared" si="6"/>
-        <v>273862.63636363635</v>
+        <v>274729.75</v>
       </c>
       <c r="O57" s="8">
         <f t="shared" si="7"/>
-        <v>15963.545454545454</v>
+        <v>15969.25</v>
       </c>
       <c r="P57" s="8">
         <f t="shared" si="8"/>
-        <v>522</v>
+        <v>580</v>
       </c>
       <c r="Q57" s="9">
         <f t="shared" si="9"/>
-        <v>17313.155172413793</v>
+        <v>17052.191379310345</v>
       </c>
       <c r="R57" s="9">
         <f t="shared" si="10"/>
-        <v>1009.1896551724137</v>
+        <v>991.19482758620688</v>
       </c>
       <c r="S57" s="10">
         <f t="shared" si="11"/>
-        <v>3.4146682150346894</v>
+        <v>3.409522640492499</v>
       </c>
       <c r="T57" s="11">
         <v>260375</v>
@@ -16113,10 +16673,24 @@
       <c r="CG57" s="13">
         <v>3.790493356580626</v>
       </c>
-      <c r="CJ57" s="11"/>
-      <c r="CK57" s="12"/>
-      <c r="CL57" s="12"/>
-      <c r="CM57" s="13"/>
+      <c r="CH57" s="11">
+        <v>284268</v>
+      </c>
+      <c r="CI57" s="11">
+        <v>16032</v>
+      </c>
+      <c r="CJ57" s="11">
+        <v>58</v>
+      </c>
+      <c r="CK57" s="12">
+        <v>14703.51724137931</v>
+      </c>
+      <c r="CL57" s="12">
+        <v>829.24137931034477</v>
+      </c>
+      <c r="CM57" s="13">
+        <v>3.3529213205284032</v>
+      </c>
     </row>
     <row r="58" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
@@ -16148,27 +16722,27 @@
       </c>
       <c r="N58" s="8">
         <f t="shared" si="6"/>
-        <v>266238.90909090912</v>
+        <v>269525.83333333331</v>
       </c>
       <c r="O58" s="8">
         <f t="shared" si="7"/>
-        <v>16935.090909090908</v>
+        <v>16718.833333333332</v>
       </c>
       <c r="P58" s="8">
         <f t="shared" si="8"/>
-        <v>514</v>
+        <v>577</v>
       </c>
       <c r="Q58" s="9">
         <f t="shared" si="9"/>
-        <v>17093.159533073929</v>
+        <v>16816.169844020798</v>
       </c>
       <c r="R58" s="9">
         <f t="shared" si="10"/>
-        <v>1087.2723735408561</v>
+        <v>1043.1161178509533</v>
       </c>
       <c r="S58" s="10">
         <f t="shared" si="11"/>
-        <v>3.5700076218073318</v>
+        <v>3.5274967256829974</v>
       </c>
       <c r="T58" s="11">
         <v>267318</v>
@@ -16368,10 +16942,24 @@
       <c r="CG58" s="13">
         <v>3.9813043077109578</v>
       </c>
-      <c r="CJ58" s="11"/>
-      <c r="CK58" s="12"/>
-      <c r="CL58" s="12"/>
-      <c r="CM58" s="13"/>
+      <c r="CH58" s="11">
+        <v>305682</v>
+      </c>
+      <c r="CI58" s="11">
+        <v>14340</v>
+      </c>
+      <c r="CJ58" s="11">
+        <v>63</v>
+      </c>
+      <c r="CK58" s="12">
+        <v>14556.285714285719</v>
+      </c>
+      <c r="CL58" s="12">
+        <v>682.85714285714289</v>
+      </c>
+      <c r="CM58" s="13">
+        <v>3.0598768683153219</v>
+      </c>
     </row>
     <row r="59" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
@@ -16403,27 +16991,27 @@
       </c>
       <c r="N59" s="8">
         <f t="shared" si="6"/>
-        <v>112212.45454545454</v>
+        <v>117765.33333333333</v>
       </c>
       <c r="O59" s="8">
         <f t="shared" si="7"/>
-        <v>24742</v>
+        <v>25810.416666666668</v>
       </c>
       <c r="P59" s="8">
         <f t="shared" si="8"/>
-        <v>287</v>
+        <v>332</v>
       </c>
       <c r="Q59" s="9">
         <f t="shared" si="9"/>
-        <v>12902.477351916375</v>
+        <v>12769.734939759037</v>
       </c>
       <c r="R59" s="9">
         <f t="shared" si="10"/>
-        <v>2844.8989547038327</v>
+        <v>2798.719879518072</v>
       </c>
       <c r="S59" s="10">
         <f t="shared" si="11"/>
-        <v>6.2852819929887662</v>
+        <v>6.277869409443114</v>
       </c>
       <c r="T59" s="11">
         <v>85293</v>
@@ -16623,10 +17211,24 @@
       <c r="CG59" s="13">
         <v>5.1135877914196124</v>
       </c>
-      <c r="CJ59" s="11"/>
-      <c r="CK59" s="12"/>
-      <c r="CL59" s="12"/>
-      <c r="CM59" s="13"/>
+      <c r="CH59" s="11">
+        <v>178847</v>
+      </c>
+      <c r="CI59" s="11">
+        <v>37563</v>
+      </c>
+      <c r="CJ59" s="11">
+        <v>45</v>
+      </c>
+      <c r="CK59" s="12">
+        <v>11923.13333333333</v>
+      </c>
+      <c r="CL59" s="12">
+        <v>2504.1999999999998</v>
+      </c>
+      <c r="CM59" s="13">
+        <v>6.196330990440944</v>
+      </c>
     </row>
     <row r="60" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
@@ -16658,27 +17260,27 @@
       </c>
       <c r="N60" s="8">
         <f t="shared" si="6"/>
-        <v>354343.18181818182</v>
+        <v>355367.91666666669</v>
       </c>
       <c r="O60" s="8">
         <f t="shared" si="7"/>
-        <v>13176.454545454546</v>
+        <v>13211.5</v>
       </c>
       <c r="P60" s="8">
         <f t="shared" si="8"/>
-        <v>436</v>
+        <v>483</v>
       </c>
       <c r="Q60" s="9">
         <f t="shared" si="9"/>
-        <v>26819.552752293581</v>
+        <v>26487.049689440992</v>
       </c>
       <c r="R60" s="9">
         <f t="shared" si="10"/>
-        <v>997.30045871559628</v>
+        <v>984.70807453416137</v>
       </c>
       <c r="S60" s="10">
         <f t="shared" si="11"/>
-        <v>2.6552381646461081</v>
+        <v>2.6548016509255992</v>
       </c>
       <c r="T60" s="11">
         <v>250720</v>
@@ -16878,10 +17480,24 @@
       <c r="CG60" s="13">
         <v>2.65</v>
       </c>
-      <c r="CJ60" s="11"/>
-      <c r="CK60" s="12"/>
-      <c r="CL60" s="12"/>
-      <c r="CM60" s="13"/>
+      <c r="CH60" s="11">
+        <v>366640</v>
+      </c>
+      <c r="CI60" s="11">
+        <v>13597</v>
+      </c>
+      <c r="CJ60" s="11">
+        <v>47</v>
+      </c>
+      <c r="CK60" s="12">
+        <v>23402.553191489362</v>
+      </c>
+      <c r="CL60" s="12">
+        <v>867.89361702127667</v>
+      </c>
+      <c r="CM60" s="13">
+        <v>2.65</v>
+      </c>
     </row>
     <row r="61" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
@@ -16913,27 +17529,27 @@
       </c>
       <c r="N61" s="8">
         <f t="shared" si="6"/>
-        <v>353377.18181818182</v>
+        <v>359159.08333333331</v>
       </c>
       <c r="O61" s="8">
         <f t="shared" si="7"/>
-        <v>13855.454545454546</v>
+        <v>14007.333333333334</v>
       </c>
       <c r="P61" s="8">
         <f t="shared" si="8"/>
-        <v>433</v>
+        <v>487</v>
       </c>
       <c r="Q61" s="9">
         <f t="shared" si="9"/>
-        <v>26931.748267898383</v>
+        <v>26549.747433264889</v>
       </c>
       <c r="R61" s="9">
         <f t="shared" si="10"/>
-        <v>1055.958429561201</v>
+        <v>1035.4496919917865</v>
       </c>
       <c r="S61" s="10">
         <f t="shared" si="11"/>
-        <v>2.7465509715916792</v>
+        <v>2.7385050572923721</v>
       </c>
       <c r="T61" s="11">
         <v>228620</v>
@@ -17133,10 +17749,24 @@
       <c r="CG61" s="13">
         <v>2.65</v>
       </c>
-      <c r="CJ61" s="11"/>
-      <c r="CK61" s="12"/>
-      <c r="CL61" s="12"/>
-      <c r="CM61" s="13"/>
+      <c r="CH61" s="11">
+        <v>422760</v>
+      </c>
+      <c r="CI61" s="11">
+        <v>15678</v>
+      </c>
+      <c r="CJ61" s="11">
+        <v>54</v>
+      </c>
+      <c r="CK61" s="12">
+        <v>23486.666666666661</v>
+      </c>
+      <c r="CL61" s="12">
+        <v>871</v>
+      </c>
+      <c r="CM61" s="13">
+        <v>2.65</v>
+      </c>
     </row>
     <row r="62" spans="1:91" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
@@ -17168,27 +17798,27 @@
       </c>
       <c r="N62" s="8">
         <f t="shared" si="6"/>
-        <v>57101.36363636364</v>
+        <v>55544.916666666664</v>
       </c>
       <c r="O62" s="8">
         <f t="shared" si="7"/>
-        <v>118263.72727272728</v>
+        <v>115773.75</v>
       </c>
       <c r="P62" s="8">
         <f t="shared" si="8"/>
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="Q62" s="9">
         <f t="shared" si="9"/>
-        <v>4919.9608355091386</v>
+        <v>4961.8287841191068</v>
       </c>
       <c r="R62" s="9">
         <f t="shared" si="10"/>
-        <v>10189.825065274152</v>
+        <v>10342.071960297766</v>
       </c>
       <c r="S62" s="10">
         <f t="shared" si="11"/>
-        <v>22.897638234625706</v>
+        <v>22.966263156692474</v>
       </c>
       <c r="T62" s="11">
         <v>63946</v>
@@ -17388,10 +18018,24 @@
       <c r="CG62" s="13">
         <v>21.73302498503142</v>
       </c>
-      <c r="CJ62" s="11"/>
-      <c r="CK62" s="12"/>
-      <c r="CL62" s="12"/>
-      <c r="CM62" s="13"/>
+      <c r="CH62" s="11">
+        <v>38424</v>
+      </c>
+      <c r="CI62" s="11">
+        <v>88384</v>
+      </c>
+      <c r="CJ62" s="11">
+        <v>20</v>
+      </c>
+      <c r="CK62" s="12">
+        <v>5763.6</v>
+      </c>
+      <c r="CL62" s="12">
+        <v>13257.6</v>
+      </c>
+      <c r="CM62" s="13">
+        <v>23.721137299426928</v>
+      </c>
     </row>
     <row r="63" spans="1:91" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
@@ -17421,11 +18065,11 @@
       <c r="M63" s="14"/>
       <c r="N63" s="14">
         <f>SUM(N3:N62)</f>
-        <v>10964259.251565656</v>
+        <v>11047871.299898989</v>
       </c>
       <c r="O63" s="14">
         <f t="shared" ref="O63" si="13">SUM(O3:O62)</f>
-        <v>2331261.6204545451</v>
+        <v>2337438.9141414147</v>
       </c>
       <c r="P63" s="14"/>
       <c r="Q63" s="14"/>
@@ -17565,11 +18209,11 @@
       <c r="CG63" s="14"/>
       <c r="CH63" s="14">
         <f>SUM(CH3:CH62)</f>
-        <v>0</v>
+        <v>11537029</v>
       </c>
       <c r="CI63" s="14">
         <f>SUM(CI3:CI62)</f>
-        <v>0</v>
+        <v>2341444</v>
       </c>
       <c r="CJ63" s="14"/>
       <c r="CK63" s="14"/>
@@ -19314,27 +19958,27 @@
       </c>
       <c r="N75" s="8">
         <f t="shared" si="14"/>
-        <v>4841401.4909090912</v>
+        <v>4949851.5333333332</v>
       </c>
       <c r="O75" s="8">
         <f t="shared" si="15"/>
-        <v>55933.909090909088</v>
+        <v>56649.416666666664</v>
       </c>
       <c r="P75" s="8">
         <f t="shared" si="16"/>
-        <v>855</v>
+        <v>938</v>
       </c>
       <c r="Q75" s="9">
         <f t="shared" si="17"/>
-        <v>186861.11017543857</v>
+        <v>189972.97995735606</v>
       </c>
       <c r="R75" s="9">
         <f t="shared" si="18"/>
-        <v>2158.8526315789472</v>
+        <v>2174.1780383795312</v>
       </c>
       <c r="S75" s="10">
         <f t="shared" si="19"/>
-        <v>1.3678976753034899</v>
+        <v>1.3627127685637701</v>
       </c>
       <c r="T75" s="11">
         <v>5178951.4000000004</v>
@@ -19534,10 +20178,24 @@
       <c r="CG75" s="13">
         <v>1.373913574768644</v>
       </c>
-      <c r="CJ75" s="11"/>
-      <c r="CK75" s="12"/>
-      <c r="CL75" s="12"/>
-      <c r="CM75" s="13"/>
+      <c r="CH75" s="11">
+        <v>6142802</v>
+      </c>
+      <c r="CI75" s="11">
+        <v>64520</v>
+      </c>
+      <c r="CJ75" s="11">
+        <v>83</v>
+      </c>
+      <c r="CK75" s="12">
+        <v>222028.98795180721</v>
+      </c>
+      <c r="CL75" s="12">
+        <v>2332.0481927710839</v>
+      </c>
+      <c r="CM75" s="13">
+        <v>1.3056787944268511</v>
+      </c>
       <c r="CN75" s="11"/>
       <c r="CO75" s="11"/>
       <c r="CP75" s="11"/>
@@ -20878,27 +21536,27 @@
       </c>
       <c r="N82" s="8">
         <f t="shared" si="14"/>
-        <v>7648129.6363636367</v>
+        <v>7834824.833333333</v>
       </c>
       <c r="O82" s="8">
         <f t="shared" si="15"/>
-        <v>13533.09090909091</v>
+        <v>13872.416666666666</v>
       </c>
       <c r="P82" s="8">
         <f t="shared" si="16"/>
-        <v>778</v>
+        <v>863</v>
       </c>
       <c r="Q82" s="9">
         <f t="shared" si="17"/>
-        <v>324406.52699228795</v>
+        <v>326829.30938586325</v>
       </c>
       <c r="R82" s="9">
         <f t="shared" si="18"/>
-        <v>574.02570694087399</v>
+        <v>578.68713789107767</v>
       </c>
       <c r="S82" s="10">
         <f t="shared" si="19"/>
-        <v>0.53104842718956879</v>
+        <v>0.5314966342522941</v>
       </c>
       <c r="T82" s="11">
         <v>5876848</v>
@@ -21098,10 +21756,24 @@
       <c r="CG82" s="13">
         <v>0.57301454121888307</v>
       </c>
-      <c r="CJ82" s="11"/>
-      <c r="CK82" s="12"/>
-      <c r="CL82" s="12"/>
-      <c r="CM82" s="13"/>
+      <c r="CH82" s="11">
+        <v>9888472</v>
+      </c>
+      <c r="CI82" s="11">
+        <v>17605</v>
+      </c>
+      <c r="CJ82" s="11">
+        <v>85</v>
+      </c>
+      <c r="CK82" s="12">
+        <v>349004.89411764703</v>
+      </c>
+      <c r="CL82" s="12">
+        <v>621.35294117647061</v>
+      </c>
+      <c r="CM82" s="13">
+        <v>0.53642691194227266</v>
+      </c>
       <c r="CN82" s="11"/>
       <c r="CO82" s="11"/>
       <c r="CP82" s="11"/>
@@ -21148,27 +21820,27 @@
       </c>
       <c r="N83" s="8">
         <f t="shared" si="14"/>
-        <v>8870186.9381818175</v>
+        <v>9040118.4433333334</v>
       </c>
       <c r="O83" s="8">
         <f t="shared" si="15"/>
-        <v>11169.727272727272</v>
+        <v>11808.166666666666</v>
       </c>
       <c r="P83" s="8">
         <f t="shared" si="16"/>
-        <v>796</v>
+        <v>882</v>
       </c>
       <c r="Q83" s="9">
         <f t="shared" si="17"/>
-        <v>367733.88060301507</v>
+        <v>368984.4262585034</v>
       </c>
       <c r="R83" s="9">
         <f t="shared" si="18"/>
-        <v>463.06658291457285</v>
+        <v>481.96598639455783</v>
       </c>
       <c r="S83" s="10">
         <f t="shared" si="19"/>
-        <v>0.454583670286479</v>
+        <v>0.46072533202659299</v>
       </c>
       <c r="T83" s="11">
         <v>8956512</v>
@@ -21368,10 +22040,24 @@
       <c r="CG83" s="13">
         <v>0.56464839722215721</v>
       </c>
-      <c r="CJ83" s="11"/>
-      <c r="CK83" s="12"/>
-      <c r="CL83" s="12"/>
-      <c r="CM83" s="13"/>
+      <c r="CH83" s="11">
+        <v>10909365</v>
+      </c>
+      <c r="CI83" s="11">
+        <v>18831</v>
+      </c>
+      <c r="CJ83" s="11">
+        <v>86</v>
+      </c>
+      <c r="CK83" s="12">
+        <v>380559.24418604648</v>
+      </c>
+      <c r="CL83" s="12">
+        <v>656.89534883720933</v>
+      </c>
+      <c r="CM83" s="13">
+        <v>0.52828361116784694</v>
+      </c>
       <c r="CN83" s="11"/>
       <c r="CO83" s="11"/>
       <c r="CP83" s="11"/>
@@ -21418,27 +22104,27 @@
       </c>
       <c r="N84" s="8">
         <f t="shared" si="14"/>
-        <v>6479462.5127272718</v>
+        <v>6899940.4699999988</v>
       </c>
       <c r="O84" s="8">
         <f t="shared" si="15"/>
-        <v>11578.818181818182</v>
+        <v>11531.166666666666</v>
       </c>
       <c r="P84" s="8">
         <f t="shared" si="16"/>
-        <v>729</v>
+        <v>804</v>
       </c>
       <c r="Q84" s="9">
         <f t="shared" si="17"/>
-        <v>293309.00263374479</v>
+        <v>308952.55835820886</v>
       </c>
       <c r="R84" s="9">
         <f t="shared" si="18"/>
-        <v>524.14403292181066</v>
+        <v>516.32089552238813</v>
       </c>
       <c r="S84" s="10">
         <f t="shared" si="19"/>
-        <v>0.52013724070034573</v>
+        <v>0.5095252851308506</v>
       </c>
       <c r="T84" s="11">
         <v>5794187</v>
@@ -21638,10 +22324,24 @@
       <c r="CG84" s="13">
         <v>0.54254379267119013</v>
       </c>
-      <c r="CJ84" s="11"/>
-      <c r="CK84" s="12"/>
-      <c r="CL84" s="12"/>
-      <c r="CM84" s="13"/>
+      <c r="CH84" s="11">
+        <v>11525198</v>
+      </c>
+      <c r="CI84" s="11">
+        <v>11007</v>
+      </c>
+      <c r="CJ84" s="11">
+        <v>75</v>
+      </c>
+      <c r="CK84" s="12">
+        <v>461007.92</v>
+      </c>
+      <c r="CL84" s="12">
+        <v>440.28</v>
+      </c>
+      <c r="CM84" s="13">
+        <v>0.39279377386640402</v>
+      </c>
       <c r="CN84" s="11"/>
       <c r="CO84" s="11"/>
       <c r="CP84" s="11"/>
@@ -21688,27 +22388,27 @@
       </c>
       <c r="N85" s="8">
         <f t="shared" si="14"/>
-        <v>6628814.5381818172</v>
+        <v>6979049.6599999992</v>
       </c>
       <c r="O85" s="8">
         <f t="shared" si="15"/>
-        <v>10216.363636363636</v>
+        <v>11615.416666666666</v>
       </c>
       <c r="P85" s="8">
         <f t="shared" si="16"/>
-        <v>730</v>
+        <v>812</v>
       </c>
       <c r="Q85" s="9">
         <f t="shared" si="17"/>
-        <v>299658.73939726019</v>
+        <v>309415.99477832508</v>
       </c>
       <c r="R85" s="9">
         <f t="shared" si="18"/>
-        <v>461.83561643835617</v>
+        <v>514.9692118226601</v>
       </c>
       <c r="S85" s="10">
         <f t="shared" si="19"/>
-        <v>0.50567007569624123</v>
+        <v>0.51628676488436975</v>
       </c>
       <c r="T85" s="11">
         <v>5905886</v>
@@ -21908,10 +22608,24 @@
       <c r="CG85" s="13">
         <v>0.39672840121414138</v>
       </c>
-      <c r="CJ85" s="11"/>
-      <c r="CK85" s="12"/>
-      <c r="CL85" s="12"/>
-      <c r="CM85" s="13"/>
+      <c r="CH85" s="11">
+        <v>10831636</v>
+      </c>
+      <c r="CI85" s="11">
+        <v>27005</v>
+      </c>
+      <c r="CJ85" s="11">
+        <v>82</v>
+      </c>
+      <c r="CK85" s="12">
+        <v>396279.36585365853</v>
+      </c>
+      <c r="CL85" s="12">
+        <v>987.98780487804879</v>
+      </c>
+      <c r="CM85" s="13">
+        <v>0.63307034595378398</v>
+      </c>
       <c r="CN85" s="11"/>
       <c r="CO85" s="11"/>
       <c r="CP85" s="11"/>
@@ -21958,27 +22672,27 @@
       </c>
       <c r="N86" s="8">
         <f t="shared" si="14"/>
-        <v>4045569.0367272724</v>
+        <v>4111189.8670000001</v>
       </c>
       <c r="O86" s="8">
         <f t="shared" si="15"/>
-        <v>9298</v>
+        <v>9623.75</v>
       </c>
       <c r="P86" s="8">
         <f t="shared" si="16"/>
-        <v>783</v>
+        <v>861</v>
       </c>
       <c r="Q86" s="9">
         <f t="shared" si="17"/>
-        <v>170502.90959386973</v>
+        <v>171896.44043205574</v>
       </c>
       <c r="R86" s="9">
         <f t="shared" si="18"/>
-        <v>391.86973180076626</v>
+        <v>402.38675958188151</v>
       </c>
       <c r="S86" s="10">
         <f t="shared" si="19"/>
-        <v>0.60683315123948656</v>
+        <v>0.6115444850894346</v>
       </c>
       <c r="T86" s="11">
         <v>3294316.2</v>
@@ -22178,10 +22892,24 @@
       <c r="CG86" s="13">
         <v>0.62875693159149304</v>
       </c>
-      <c r="CJ86" s="11"/>
-      <c r="CK86" s="12"/>
-      <c r="CL86" s="12"/>
-      <c r="CM86" s="13"/>
+      <c r="CH86" s="11">
+        <v>4833019</v>
+      </c>
+      <c r="CI86" s="11">
+        <v>13207</v>
+      </c>
+      <c r="CJ86" s="11">
+        <v>78</v>
+      </c>
+      <c r="CK86" s="12">
+        <v>185885.34615384621</v>
+      </c>
+      <c r="CL86" s="12">
+        <v>507.96153846153851</v>
+      </c>
+      <c r="CM86" s="13">
+        <v>0.66336915743886216</v>
+      </c>
       <c r="CN86" s="11"/>
       <c r="CO86" s="11"/>
       <c r="CP86" s="11"/>
@@ -22228,27 +22956,27 @@
       </c>
       <c r="N87" s="8">
         <f t="shared" si="14"/>
-        <v>4636881.47</v>
+        <v>4730097.7641666671</v>
       </c>
       <c r="O87" s="8">
         <f t="shared" si="15"/>
-        <v>11950.90909090909</v>
+        <v>12089</v>
       </c>
       <c r="P87" s="8">
         <f t="shared" si="16"/>
-        <v>778</v>
+        <v>855</v>
       </c>
       <c r="Q87" s="9">
         <f t="shared" si="17"/>
-        <v>196680.06235218508</v>
+        <v>199162.01112280702</v>
       </c>
       <c r="R87" s="9">
         <f t="shared" si="18"/>
-        <v>506.91516709511575</v>
+        <v>509.01052631578943</v>
       </c>
       <c r="S87" s="10">
         <f t="shared" si="19"/>
-        <v>0.64647992442261726</v>
+        <v>0.64410768495977966</v>
       </c>
       <c r="T87" s="11">
         <v>3330630</v>
@@ -22448,10 +23176,24 @@
       <c r="CG87" s="13">
         <v>0.62533291810204872</v>
       </c>
-      <c r="CJ87" s="11"/>
-      <c r="CK87" s="12"/>
-      <c r="CL87" s="12"/>
-      <c r="CM87" s="13"/>
+      <c r="CH87" s="11">
+        <v>5755477</v>
+      </c>
+      <c r="CI87" s="11">
+        <v>13608</v>
+      </c>
+      <c r="CJ87" s="11">
+        <v>77</v>
+      </c>
+      <c r="CK87" s="12">
+        <v>224239.36363636359</v>
+      </c>
+      <c r="CL87" s="12">
+        <v>530.18181818181813</v>
+      </c>
+      <c r="CM87" s="13">
+        <v>0.61801305086856673</v>
+      </c>
       <c r="CN87" s="11"/>
       <c r="CO87" s="11"/>
       <c r="CP87" s="11"/>
@@ -22498,27 +23240,27 @@
       </c>
       <c r="N88" s="8">
         <f t="shared" si="14"/>
-        <v>3692007.7214545459</v>
+        <v>3776781.3280000002</v>
       </c>
       <c r="O88" s="8">
         <f t="shared" si="15"/>
-        <v>9453.818181818182</v>
+        <v>9741.8333333333339</v>
       </c>
       <c r="P88" s="8">
         <f t="shared" si="16"/>
-        <v>778</v>
+        <v>857</v>
       </c>
       <c r="Q88" s="9">
         <f t="shared" si="17"/>
-        <v>156601.86993316197</v>
+        <v>158651.25765227538</v>
       </c>
       <c r="R88" s="9">
         <f t="shared" si="18"/>
-        <v>400.99742930591259</v>
+        <v>409.22520420070009</v>
       </c>
       <c r="S88" s="10">
         <f t="shared" si="19"/>
-        <v>0.64002194896263453</v>
+        <v>0.64215335184877353</v>
       </c>
       <c r="T88" s="11">
         <v>3521856</v>
@@ -22718,10 +23460,24 @@
       <c r="CG88" s="13">
         <v>0.6482773277705427</v>
       </c>
-      <c r="CJ88" s="11"/>
-      <c r="CK88" s="12"/>
-      <c r="CL88" s="12"/>
-      <c r="CM88" s="13"/>
+      <c r="CH88" s="11">
+        <v>4709291</v>
+      </c>
+      <c r="CI88" s="11">
+        <v>12910</v>
+      </c>
+      <c r="CJ88" s="11">
+        <v>79</v>
+      </c>
+      <c r="CK88" s="12">
+        <v>178833.835443038</v>
+      </c>
+      <c r="CL88" s="12">
+        <v>490.25316455696202</v>
+      </c>
+      <c r="CM88" s="13">
+        <v>0.66559878359630265</v>
+      </c>
       <c r="CN88" s="11"/>
       <c r="CO88" s="11"/>
       <c r="CP88" s="11"/>
@@ -23542,27 +24298,27 @@
       </c>
       <c r="N92" s="8">
         <f t="shared" si="14"/>
-        <v>8707874.1818181816</v>
+        <v>8981430</v>
       </c>
       <c r="O92" s="8">
         <f t="shared" si="15"/>
-        <v>13634.454545454546</v>
+        <v>13848.666666666666</v>
       </c>
       <c r="P92" s="8">
         <f t="shared" si="16"/>
-        <v>787</v>
+        <v>871</v>
       </c>
       <c r="Q92" s="9">
         <f t="shared" si="17"/>
-        <v>365133.2249047014</v>
+        <v>371218.69115958665</v>
       </c>
       <c r="R92" s="9">
         <f t="shared" si="18"/>
-        <v>571.71156289707756</v>
+        <v>572.39035591274398</v>
       </c>
       <c r="S92" s="10">
         <f t="shared" si="19"/>
-        <v>0.50692762295830418</v>
+        <v>0.50363780200739128</v>
       </c>
       <c r="T92" s="11">
         <v>9900279</v>
@@ -23762,10 +24518,24 @@
       <c r="CG92" s="13">
         <v>0.5027638089151284</v>
       </c>
-      <c r="CJ92" s="11"/>
-      <c r="CK92" s="12"/>
-      <c r="CL92" s="12"/>
-      <c r="CM92" s="13"/>
+      <c r="CH92" s="11">
+        <v>11990544</v>
+      </c>
+      <c r="CI92" s="11">
+        <v>16205</v>
+      </c>
+      <c r="CJ92" s="11">
+        <v>84</v>
+      </c>
+      <c r="CK92" s="12">
+        <v>428233.71428571432</v>
+      </c>
+      <c r="CL92" s="12">
+        <v>578.75</v>
+      </c>
+      <c r="CM92" s="13">
+        <v>0.46744977154734901</v>
+      </c>
       <c r="CN92" s="11"/>
       <c r="CO92" s="11"/>
       <c r="CP92" s="11"/>
@@ -23812,27 +24582,27 @@
       </c>
       <c r="N93" s="8">
         <f t="shared" si="14"/>
-        <v>5643479.8372727279</v>
+        <v>5968519.600833334</v>
       </c>
       <c r="O93" s="8">
         <f t="shared" si="15"/>
-        <v>9080.181818181818</v>
+        <v>10015.75</v>
       </c>
       <c r="P93" s="8">
         <f t="shared" si="16"/>
-        <v>746</v>
+        <v>824</v>
       </c>
       <c r="Q93" s="9">
         <f t="shared" si="17"/>
-        <v>249644.55044235929</v>
+        <v>260760.56508495146</v>
       </c>
       <c r="R93" s="9">
         <f t="shared" si="18"/>
-        <v>401.6702412868633</v>
+        <v>437.58131067961165</v>
       </c>
       <c r="S93" s="10">
         <f t="shared" si="19"/>
-        <v>0.49066424109490908</v>
+        <v>0.49854490012754377</v>
       </c>
       <c r="T93" s="11">
         <v>2929766.3999999999</v>
@@ -24032,10 +24802,24 @@
       <c r="CG93" s="13">
         <v>0.54814707859325684</v>
       </c>
-      <c r="CJ93" s="11"/>
-      <c r="CK93" s="12"/>
-      <c r="CL93" s="12"/>
-      <c r="CM93" s="13"/>
+      <c r="CH93" s="11">
+        <v>9543957</v>
+      </c>
+      <c r="CI93" s="11">
+        <v>20307</v>
+      </c>
+      <c r="CJ93" s="11">
+        <v>78</v>
+      </c>
+      <c r="CK93" s="12">
+        <v>367075.26923076919</v>
+      </c>
+      <c r="CL93" s="12">
+        <v>781.03846153846166</v>
+      </c>
+      <c r="CM93" s="13">
+        <v>0.5852321494865258</v>
+      </c>
       <c r="CN93" s="11"/>
       <c r="CO93" s="11"/>
       <c r="CP93" s="11"/>
@@ -24218,27 +25002,27 @@
       </c>
       <c r="N95" s="8">
         <f t="shared" si="14"/>
-        <v>1233286.499090909</v>
+        <v>1247045.4158333333</v>
       </c>
       <c r="O95" s="8">
         <f t="shared" si="15"/>
-        <v>169380.72727272726</v>
+        <v>170617.75</v>
       </c>
       <c r="P95" s="8">
         <f t="shared" si="16"/>
-        <v>800</v>
+        <v>881</v>
       </c>
       <c r="Q95" s="9">
         <f t="shared" si="17"/>
-        <v>50873.068087499996</v>
+        <v>50957.58793416572</v>
       </c>
       <c r="R95" s="9">
         <f t="shared" si="18"/>
-        <v>6986.9549999999999</v>
+        <v>6971.894438138479</v>
       </c>
       <c r="S95" s="10">
         <f t="shared" si="19"/>
-        <v>4.7770728045703716</v>
+        <v>4.7641286374107583</v>
       </c>
       <c r="T95" s="11">
         <v>1330711.48</v>
@@ -24438,10 +25222,24 @@
       <c r="CG95" s="13">
         <v>4.8870036176513336</v>
       </c>
-      <c r="CJ95" s="11"/>
-      <c r="CK95" s="12"/>
-      <c r="CL95" s="12"/>
-      <c r="CM95" s="13"/>
+      <c r="CH95" s="11">
+        <v>1398393.5</v>
+      </c>
+      <c r="CI95" s="11">
+        <v>184225</v>
+      </c>
+      <c r="CJ95" s="11">
+        <v>81</v>
+      </c>
+      <c r="CK95" s="12">
+        <v>51792.351851851847</v>
+      </c>
+      <c r="CL95" s="12">
+        <v>6823.1481481481487</v>
+      </c>
+      <c r="CM95" s="13">
+        <v>4.6217427986550161</v>
+      </c>
       <c r="CN95" s="11"/>
       <c r="CO95" s="11"/>
       <c r="CP95" s="11"/>
@@ -24488,27 +25286,27 @@
       </c>
       <c r="N96" s="8">
         <f t="shared" si="14"/>
-        <v>3164422.0363636361</v>
+        <v>3203861.0333333332</v>
       </c>
       <c r="O96" s="8">
         <f t="shared" si="15"/>
-        <v>53450.181818181816</v>
+        <v>53814.25</v>
       </c>
       <c r="P96" s="8">
         <f t="shared" si="16"/>
-        <v>829</v>
+        <v>909</v>
       </c>
       <c r="Q96" s="9">
         <f t="shared" si="17"/>
-        <v>125966.1365500603</v>
+        <v>126885.58547854784</v>
       </c>
       <c r="R96" s="9">
         <f t="shared" si="18"/>
-        <v>2127.6911942098914</v>
+        <v>2131.257425742574</v>
       </c>
       <c r="S96" s="10">
         <f t="shared" si="19"/>
-        <v>1.6575952352691343</v>
+        <v>1.6531993240246292</v>
       </c>
       <c r="T96" s="11">
         <v>3147444.45</v>
@@ -24708,10 +25506,24 @@
       <c r="CG96" s="13">
         <v>1.719379096063147</v>
       </c>
-      <c r="CJ96" s="11"/>
-      <c r="CK96" s="12"/>
-      <c r="CL96" s="12"/>
-      <c r="CM96" s="13"/>
+      <c r="CH96" s="11">
+        <v>3637690</v>
+      </c>
+      <c r="CI96" s="11">
+        <v>57819</v>
+      </c>
+      <c r="CJ96" s="11">
+        <v>80</v>
+      </c>
+      <c r="CK96" s="12">
+        <v>136413.375</v>
+      </c>
+      <c r="CL96" s="12">
+        <v>2168.2125000000001</v>
+      </c>
+      <c r="CM96" s="13">
+        <v>1.604844300335073</v>
+      </c>
       <c r="CN96" s="11"/>
       <c r="CO96" s="11"/>
       <c r="CP96" s="11"/>
@@ -24758,27 +25570,27 @@
       </c>
       <c r="N97" s="8">
         <f t="shared" si="14"/>
-        <v>4670339.9090909092</v>
+        <v>4738325.25</v>
       </c>
       <c r="O97" s="8">
         <f t="shared" si="15"/>
-        <v>22483.18181818182</v>
+        <v>22899.083333333332</v>
       </c>
       <c r="P97" s="8">
         <f t="shared" si="16"/>
-        <v>853</v>
+        <v>938</v>
       </c>
       <c r="Q97" s="9">
         <f t="shared" si="17"/>
-        <v>180681.37983587341</v>
+        <v>181854.70042643923</v>
       </c>
       <c r="R97" s="9">
         <f t="shared" si="18"/>
-        <v>869.80656506447826</v>
+        <v>878.85607675906181</v>
       </c>
       <c r="S97" s="10">
         <f t="shared" si="19"/>
-        <v>0.88184514226560851</v>
+        <v>0.88337166377778142</v>
       </c>
       <c r="T97" s="11">
         <v>4665522</v>
@@ -24978,10 +25790,24 @@
       <c r="CG97" s="13">
         <v>0.87341471003601723</v>
       </c>
-      <c r="CJ97" s="11"/>
-      <c r="CK97" s="12"/>
-      <c r="CL97" s="12"/>
-      <c r="CM97" s="13"/>
+      <c r="CH97" s="11">
+        <v>5486164</v>
+      </c>
+      <c r="CI97" s="11">
+        <v>27474</v>
+      </c>
+      <c r="CJ97" s="11">
+        <v>85</v>
+      </c>
+      <c r="CK97" s="12">
+        <v>193629.31764705881</v>
+      </c>
+      <c r="CL97" s="12">
+        <v>969.67058823529419</v>
+      </c>
+      <c r="CM97" s="13">
+        <v>0.90016340041168386</v>
+      </c>
       <c r="CN97" s="11"/>
       <c r="CO97" s="11"/>
       <c r="CP97" s="11"/>
@@ -25028,27 +25854,27 @@
       </c>
       <c r="N98" s="8">
         <f t="shared" si="14"/>
-        <v>5551857.3636363633</v>
+        <v>5569667.5</v>
       </c>
       <c r="O98" s="8">
         <f t="shared" si="15"/>
-        <v>37368</v>
+        <v>37131.25</v>
       </c>
       <c r="P98" s="8">
         <f t="shared" si="16"/>
-        <v>857</v>
+        <v>940</v>
       </c>
       <c r="Q98" s="9">
         <f t="shared" si="17"/>
-        <v>213782.13885647606</v>
+        <v>213306.41489361704</v>
       </c>
       <c r="R98" s="9">
         <f t="shared" si="18"/>
-        <v>1438.9078179696617</v>
+        <v>1422.0478723404256</v>
       </c>
       <c r="S98" s="10">
         <f t="shared" si="19"/>
-        <v>1.0420653074593949</v>
+        <v>1.0372254410827408</v>
       </c>
       <c r="T98" s="11">
         <v>5106248</v>
@@ -25248,10 +26074,24 @@
       <c r="CG98" s="13">
         <v>1.0240933937456931</v>
       </c>
-      <c r="CJ98" s="11"/>
-      <c r="CK98" s="12"/>
-      <c r="CL98" s="12"/>
-      <c r="CM98" s="13"/>
+      <c r="CH98" s="11">
+        <v>5765579</v>
+      </c>
+      <c r="CI98" s="11">
+        <v>34527</v>
+      </c>
+      <c r="CJ98" s="11">
+        <v>83</v>
+      </c>
+      <c r="CK98" s="12">
+        <v>208394.42168674699</v>
+      </c>
+      <c r="CL98" s="12">
+        <v>1247.963855421687</v>
+      </c>
+      <c r="CM98" s="13">
+        <v>0.98398691093954604</v>
+      </c>
       <c r="CN98" s="11"/>
       <c r="CO98" s="11"/>
       <c r="CP98" s="11"/>
@@ -25298,27 +26138,27 @@
       </c>
       <c r="N99" s="8">
         <f t="shared" ref="N99:N132" si="20">IFERROR(AVERAGE(T99,Z99,AF99,AL99,AR99,AX99,BD99,BJ99,BP99,BV99,CB99,CH99)," ")</f>
-        <v>5638737.0909090908</v>
+        <v>5641589.916666667</v>
       </c>
       <c r="O99" s="8">
         <f t="shared" ref="O99:O132" si="21">IFERROR(AVERAGE(U99,AA99,AG99,AM99,AS99,AY99,BE99,BK99,BQ99,BW99,CC99,CI99)," ")</f>
-        <v>35638.818181818184</v>
+        <v>36041.5</v>
       </c>
       <c r="P99" s="8">
         <f t="shared" ref="P99:P132" si="22">IFERROR(SUM(V99,AB99,AH99,AN99,AT99,AZ99,BF99,BL99,BR99,BX99,CD99,CJ99)," ")</f>
-        <v>854</v>
+        <v>937</v>
       </c>
       <c r="Q99" s="9">
         <f t="shared" ref="Q99:Q130" si="23">IFERROR(SUM(T99,Z99,AF99,AL99,AR99,AX99,BD99,BJ99,BP99,BV99,CB99,CH99)/P99*3," ")</f>
-        <v>217890.30913348944</v>
+        <v>216752.65421558163</v>
       </c>
       <c r="R99" s="9">
         <f t="shared" ref="R99:R132" si="24">IFERROR(SUM(U99,AA99,AG99,AM99,AS99,AY99,BE99,BK99,BQ99,BW99,CC99,CI99)/P99*3," ")</f>
-        <v>1377.1440281030445</v>
+        <v>1384.7321237993597</v>
       </c>
       <c r="S99" s="10">
         <f t="shared" ref="S99:S132" si="25">IFERROR(AVERAGE(Y99,AE99,AK99,AQ99,AW99,BC99,BI99,BO99,BU99,CA99,CG99,CM99)," ")</f>
-        <v>1.0028484251076837</v>
+        <v>1.0089089736613723</v>
       </c>
       <c r="T99" s="11">
         <v>5194966</v>
@@ -25518,10 +26358,24 @@
       <c r="CG99" s="13">
         <v>1.0093902207482921</v>
       </c>
-      <c r="CJ99" s="11"/>
-      <c r="CK99" s="12"/>
-      <c r="CL99" s="12"/>
-      <c r="CM99" s="13"/>
+      <c r="CH99" s="11">
+        <v>5672971</v>
+      </c>
+      <c r="CI99" s="11">
+        <v>40471</v>
+      </c>
+      <c r="CJ99" s="11">
+        <v>83</v>
+      </c>
+      <c r="CK99" s="12">
+        <v>205047.14457831319</v>
+      </c>
+      <c r="CL99" s="12">
+        <v>1462.807228915663</v>
+      </c>
+      <c r="CM99" s="13">
+        <v>1.0755750077519479</v>
+      </c>
       <c r="CN99" s="11"/>
       <c r="CO99" s="11"/>
       <c r="CP99" s="11"/>
@@ -25568,27 +26422,27 @@
       </c>
       <c r="N100" s="8">
         <f t="shared" si="20"/>
-        <v>4220573.7272727275</v>
+        <v>4141226.5</v>
       </c>
       <c r="O100" s="8">
         <f t="shared" si="21"/>
-        <v>141613.54545454544</v>
+        <v>140008.5</v>
       </c>
       <c r="P100" s="8">
         <f t="shared" si="22"/>
-        <v>724</v>
+        <v>785</v>
       </c>
       <c r="Q100" s="9">
         <f t="shared" si="23"/>
-        <v>192374.21685082873</v>
+        <v>189916.11974522294</v>
       </c>
       <c r="R100" s="9">
         <f t="shared" si="24"/>
-        <v>6454.7610497237565</v>
+        <v>6420.771974522293</v>
       </c>
       <c r="S100" s="10">
         <f t="shared" si="25"/>
-        <v>2.3376921032734455</v>
+        <v>2.3481481377776379</v>
       </c>
       <c r="T100" s="11">
         <v>4112013</v>
@@ -25788,10 +26642,24 @@
       <c r="CG100" s="13">
         <v>2.4320118569403228</v>
       </c>
-      <c r="CJ100" s="11"/>
-      <c r="CK100" s="12"/>
-      <c r="CL100" s="12"/>
-      <c r="CM100" s="13"/>
+      <c r="CH100" s="11">
+        <v>3268407</v>
+      </c>
+      <c r="CI100" s="11">
+        <v>122353</v>
+      </c>
+      <c r="CJ100" s="11">
+        <v>61</v>
+      </c>
+      <c r="CK100" s="12">
+        <v>160741.32786885239</v>
+      </c>
+      <c r="CL100" s="12">
+        <v>6017.3606557377052</v>
+      </c>
+      <c r="CM100" s="13">
+        <v>2.46316451732375</v>
+      </c>
       <c r="CN100" s="11"/>
       <c r="CO100" s="11"/>
       <c r="CP100" s="11"/>
@@ -25838,27 +26706,27 @@
       </c>
       <c r="N101" s="8">
         <f t="shared" si="20"/>
-        <v>3833856.0909090908</v>
+        <v>3831127.9166666665</v>
       </c>
       <c r="O101" s="8">
         <f t="shared" si="21"/>
-        <v>72910.636363636368</v>
+        <v>72005.166666666672</v>
       </c>
       <c r="P101" s="8">
         <f t="shared" si="22"/>
-        <v>844</v>
+        <v>923</v>
       </c>
       <c r="Q101" s="9">
         <f t="shared" si="23"/>
-        <v>149901.95616113744</v>
+        <v>149426.44095341279</v>
       </c>
       <c r="R101" s="9">
         <f t="shared" si="24"/>
-        <v>2850.7713270142181</v>
+        <v>2808.4355362946912</v>
       </c>
       <c r="S101" s="10">
         <f t="shared" si="25"/>
-        <v>1.7488642262260969</v>
+        <v>1.7386080953893102</v>
       </c>
       <c r="T101" s="11">
         <v>4799841</v>
@@ -26058,10 +26926,24 @@
       <c r="CG101" s="13">
         <v>1.758046862447904</v>
       </c>
-      <c r="CJ101" s="11"/>
-      <c r="CK101" s="12"/>
-      <c r="CL101" s="12"/>
-      <c r="CM101" s="13"/>
+      <c r="CH101" s="11">
+        <v>3801118</v>
+      </c>
+      <c r="CI101" s="11">
+        <v>62045</v>
+      </c>
+      <c r="CJ101" s="11">
+        <v>79</v>
+      </c>
+      <c r="CK101" s="12">
+        <v>144346.25316455701</v>
+      </c>
+      <c r="CL101" s="12">
+        <v>2356.1392405063289</v>
+      </c>
+      <c r="CM101" s="13">
+        <v>1.625790656184654</v>
+      </c>
       <c r="CN101" s="11"/>
       <c r="CO101" s="11"/>
       <c r="CP101" s="11"/>
@@ -26108,27 +26990,27 @@
       </c>
       <c r="N102" s="8">
         <f t="shared" si="20"/>
-        <v>3875024.9040609342</v>
+        <v>3858268.4120558561</v>
       </c>
       <c r="O102" s="8">
         <f t="shared" si="21"/>
-        <v>69221.545454545456</v>
+        <v>69176.416666666672</v>
       </c>
       <c r="P102" s="8">
         <f t="shared" si="22"/>
-        <v>844</v>
+        <v>925</v>
       </c>
       <c r="Q102" s="9">
         <f t="shared" si="23"/>
-        <v>151511.63724408866</v>
+        <v>150159.63549622794</v>
       </c>
       <c r="R102" s="9">
         <f t="shared" si="24"/>
-        <v>2706.5296208530804</v>
+        <v>2692.2713513513513</v>
       </c>
       <c r="S102" s="10">
         <f t="shared" si="25"/>
-        <v>1.6988476664265344</v>
+        <v>1.7023478178981708</v>
       </c>
       <c r="T102" s="11">
         <v>3557596</v>
@@ -26328,10 +27210,24 @@
       <c r="CG102" s="13">
         <v>1.660700660563837</v>
       </c>
-      <c r="CJ102" s="11"/>
-      <c r="CK102" s="12"/>
-      <c r="CL102" s="12"/>
-      <c r="CM102" s="13"/>
+      <c r="CH102" s="11">
+        <v>3673947</v>
+      </c>
+      <c r="CI102" s="11">
+        <v>68680</v>
+      </c>
+      <c r="CJ102" s="11">
+        <v>81</v>
+      </c>
+      <c r="CK102" s="12">
+        <v>136072.11111111109</v>
+      </c>
+      <c r="CL102" s="12">
+        <v>2543.7037037037039</v>
+      </c>
+      <c r="CM102" s="13">
+        <v>1.7408494840861699</v>
+      </c>
       <c r="CN102" s="11"/>
       <c r="CO102" s="11"/>
       <c r="CP102" s="11"/>
@@ -26378,27 +27274,27 @@
       </c>
       <c r="N103" s="8">
         <f t="shared" si="20"/>
-        <v>3507045.8789181816</v>
+        <v>3469482.6140083335</v>
       </c>
       <c r="O103" s="8">
         <f t="shared" si="21"/>
-        <v>84557</v>
+        <v>84374.416666666672</v>
       </c>
       <c r="P103" s="8">
         <f t="shared" si="22"/>
-        <v>838</v>
+        <v>917</v>
       </c>
       <c r="Q103" s="9">
         <f t="shared" si="23"/>
-        <v>138105.62530346061</v>
+        <v>136206.51483565976</v>
       </c>
       <c r="R103" s="9">
         <f t="shared" si="24"/>
-        <v>3329.8102625298329</v>
+        <v>3312.4089422028351</v>
       </c>
       <c r="S103" s="10">
         <f t="shared" si="25"/>
-        <v>1.9840013997558186</v>
+        <v>1.9928646382481841</v>
       </c>
       <c r="T103" s="11">
         <v>3372981.7431000001</v>
@@ -26598,10 +27494,24 @@
       <c r="CG103" s="13">
         <v>2.0517004993776609</v>
       </c>
-      <c r="CJ103" s="11"/>
-      <c r="CK103" s="12"/>
-      <c r="CL103" s="12"/>
-      <c r="CM103" s="13"/>
+      <c r="CH103" s="11">
+        <v>3056286.7</v>
+      </c>
+      <c r="CI103" s="11">
+        <v>82366</v>
+      </c>
+      <c r="CJ103" s="11">
+        <v>79</v>
+      </c>
+      <c r="CK103" s="12">
+        <v>116061.5202531645</v>
+      </c>
+      <c r="CL103" s="12">
+        <v>3127.8227848101269</v>
+      </c>
+      <c r="CM103" s="13">
+        <v>2.090360261664205</v>
+      </c>
       <c r="CN103" s="11"/>
       <c r="CO103" s="11"/>
       <c r="CP103" s="11"/>
@@ -26648,27 +27558,27 @@
       </c>
       <c r="N104" s="8">
         <f t="shared" si="20"/>
-        <v>2078975.3745454543</v>
+        <v>2136366.9266666663</v>
       </c>
       <c r="O104" s="8">
         <f t="shared" si="21"/>
-        <v>164365.81818181818</v>
+        <v>167087.91666666666</v>
       </c>
       <c r="P104" s="8">
         <f t="shared" si="22"/>
-        <v>846</v>
+        <v>928</v>
       </c>
       <c r="Q104" s="9">
         <f t="shared" si="23"/>
-        <v>81094.784113475165</v>
+        <v>82876.303189655169</v>
       </c>
       <c r="R104" s="9">
         <f t="shared" si="24"/>
-        <v>6411.432624113475</v>
+        <v>6481.8588362068967</v>
       </c>
       <c r="S104" s="10">
         <f t="shared" si="25"/>
-        <v>3.5921020820477554</v>
+        <v>3.5758600071677438</v>
       </c>
       <c r="T104" s="11">
         <v>2131852.875</v>
@@ -26868,10 +27778,24 @@
       <c r="CG104" s="13">
         <v>3.4659551904343782</v>
       </c>
-      <c r="CJ104" s="11"/>
-      <c r="CK104" s="12"/>
-      <c r="CL104" s="12"/>
-      <c r="CM104" s="13"/>
+      <c r="CH104" s="11">
+        <v>2767674</v>
+      </c>
+      <c r="CI104" s="11">
+        <v>197031</v>
+      </c>
+      <c r="CJ104" s="11">
+        <v>82</v>
+      </c>
+      <c r="CK104" s="12">
+        <v>101256.3658536585</v>
+      </c>
+      <c r="CL104" s="12">
+        <v>7208.4512195121952</v>
+      </c>
+      <c r="CM104" s="13">
+        <v>3.3971971834876098</v>
+      </c>
       <c r="CN104" s="11"/>
       <c r="CO104" s="11"/>
       <c r="CP104" s="11"/>
@@ -26918,27 +27842,27 @@
       </c>
       <c r="N105" s="8">
         <f t="shared" si="20"/>
-        <v>1741391.0649999999</v>
+        <v>1714653.3741666665</v>
       </c>
       <c r="O105" s="8">
         <f t="shared" si="21"/>
-        <v>133831.72727272726</v>
+        <v>134124.75</v>
       </c>
       <c r="P105" s="8">
         <f t="shared" si="22"/>
-        <v>817</v>
+        <v>898</v>
       </c>
       <c r="Q105" s="9">
         <f t="shared" si="23"/>
-        <v>70337.70519583844</v>
+        <v>68738.888051224945</v>
       </c>
       <c r="R105" s="9">
         <f t="shared" si="24"/>
-        <v>5405.6878824969408</v>
+        <v>5376.9387527839644</v>
       </c>
       <c r="S105" s="10">
         <f t="shared" si="25"/>
-        <v>3.5511642699121135</v>
+        <v>3.585173670369953</v>
       </c>
       <c r="T105" s="11">
         <v>1866502.7749999999</v>
@@ -27138,10 +28062,24 @@
       <c r="CG105" s="13">
         <v>4.1285562454675224</v>
       </c>
-      <c r="CJ105" s="11"/>
-      <c r="CK105" s="12"/>
-      <c r="CL105" s="12"/>
-      <c r="CM105" s="13"/>
+      <c r="CH105" s="11">
+        <v>1420538.7749999999</v>
+      </c>
+      <c r="CI105" s="11">
+        <v>137348</v>
+      </c>
+      <c r="CJ105" s="11">
+        <v>81</v>
+      </c>
+      <c r="CK105" s="12">
+        <v>52612.547222222223</v>
+      </c>
+      <c r="CL105" s="12">
+        <v>5086.9629629629626</v>
+      </c>
+      <c r="CM105" s="13">
+        <v>3.959277075406189</v>
+      </c>
       <c r="CN105" s="11"/>
       <c r="CO105" s="11"/>
       <c r="CP105" s="11"/>
@@ -27188,27 +28126,27 @@
       </c>
       <c r="N106" s="8">
         <f t="shared" si="20"/>
-        <v>2803354.9280000003</v>
+        <v>2858588.3027272727</v>
       </c>
       <c r="O106" s="8">
         <f t="shared" si="21"/>
-        <v>74342.3</v>
+        <v>74606.363636363632</v>
       </c>
       <c r="P106" s="8">
         <f t="shared" si="22"/>
-        <v>689</v>
+        <v>770</v>
       </c>
       <c r="Q106" s="9">
         <f t="shared" si="23"/>
-        <v>122061.8981712627</v>
+        <v>122510.92725974027</v>
       </c>
       <c r="R106" s="9">
         <f t="shared" si="24"/>
-        <v>3236.9651669085633</v>
+        <v>3197.4155844155844</v>
       </c>
       <c r="S106" s="10">
         <f t="shared" si="25"/>
-        <v>2.1146433019709594</v>
+        <v>2.0964973562410476</v>
       </c>
       <c r="T106" s="11">
         <v>742431.28</v>
@@ -27396,10 +28334,24 @@
       <c r="CG106" s="13">
         <v>2.0796602652185618</v>
       </c>
-      <c r="CJ106" s="11"/>
-      <c r="CK106" s="12"/>
-      <c r="CL106" s="12"/>
-      <c r="CM106" s="13"/>
+      <c r="CH106" s="11">
+        <v>3410922.05</v>
+      </c>
+      <c r="CI106" s="11">
+        <v>77247</v>
+      </c>
+      <c r="CJ106" s="11">
+        <v>81</v>
+      </c>
+      <c r="CK106" s="12">
+        <v>126330.4462962963</v>
+      </c>
+      <c r="CL106" s="12">
+        <v>2861</v>
+      </c>
+      <c r="CM106" s="13">
+        <v>1.9150378989419281</v>
+      </c>
       <c r="CN106" s="11"/>
       <c r="CO106" s="11"/>
       <c r="CP106" s="11"/>
@@ -27582,27 +28534,27 @@
       </c>
       <c r="N108" s="8">
         <f t="shared" si="20"/>
-        <v>3390411.4249999998</v>
+        <v>3393701.5681818184</v>
       </c>
       <c r="O108" s="8">
         <f t="shared" si="21"/>
-        <v>76574.600000000006</v>
+        <v>76366.181818181823</v>
       </c>
       <c r="P108" s="8">
         <f t="shared" si="22"/>
-        <v>771</v>
+        <v>848</v>
       </c>
       <c r="Q108" s="9">
         <f t="shared" si="23"/>
-        <v>131922.62354085603</v>
+        <v>132066.21668632075</v>
       </c>
       <c r="R108" s="9">
         <f t="shared" si="24"/>
-        <v>2979.5564202334631</v>
+        <v>2971.7971698113206</v>
       </c>
       <c r="S108" s="10">
         <f t="shared" si="25"/>
-        <v>1.9250873973886642</v>
+        <v>1.9203217147454021</v>
       </c>
       <c r="T108" s="11">
         <v>3195378.4</v>
@@ -27790,10 +28742,24 @@
       <c r="CG108" s="13">
         <v>1.870686478636997</v>
       </c>
-      <c r="CJ108" s="11"/>
-      <c r="CK108" s="12"/>
-      <c r="CL108" s="12"/>
-      <c r="CM108" s="13"/>
+      <c r="CH108" s="11">
+        <v>3426603</v>
+      </c>
+      <c r="CI108" s="11">
+        <v>74282</v>
+      </c>
+      <c r="CJ108" s="11">
+        <v>77</v>
+      </c>
+      <c r="CK108" s="12">
+        <v>133504.012987013</v>
+      </c>
+      <c r="CL108" s="12">
+        <v>2894.1038961038962</v>
+      </c>
+      <c r="CM108" s="13">
+        <v>1.872664888312783</v>
+      </c>
       <c r="CN108" s="11"/>
       <c r="CO108" s="11"/>
       <c r="CP108" s="11"/>
@@ -27840,27 +28806,27 @@
       </c>
       <c r="N109" s="8">
         <f t="shared" si="20"/>
-        <v>2780750.8863636362</v>
+        <v>2778667.1625000001</v>
       </c>
       <c r="O109" s="8">
         <f t="shared" si="21"/>
-        <v>75845.909090909088</v>
+        <v>75774.416666666672</v>
       </c>
       <c r="P109" s="8">
         <f t="shared" si="22"/>
-        <v>843</v>
+        <v>921</v>
       </c>
       <c r="Q109" s="9">
         <f t="shared" si="23"/>
-        <v>108855.0169039146</v>
+        <v>108612.39723127036</v>
       </c>
       <c r="R109" s="9">
         <f t="shared" si="24"/>
-        <v>2969.0569395017792</v>
+        <v>2961.8664495114008</v>
       </c>
       <c r="S109" s="10">
         <f t="shared" si="25"/>
-        <v>2.1205676897802856</v>
+        <v>2.1186913572689599</v>
       </c>
       <c r="T109" s="11">
         <v>2534506.75</v>
@@ -28060,10 +29026,24 @@
       <c r="CG109" s="13">
         <v>1.8614813652912909</v>
       </c>
-      <c r="CJ109" s="11"/>
-      <c r="CK109" s="12"/>
-      <c r="CL109" s="12"/>
-      <c r="CM109" s="13"/>
+      <c r="CH109" s="11">
+        <v>2755746.2</v>
+      </c>
+      <c r="CI109" s="11">
+        <v>74988</v>
+      </c>
+      <c r="CJ109" s="11">
+        <v>78</v>
+      </c>
+      <c r="CK109" s="12">
+        <v>105990.23846153849</v>
+      </c>
+      <c r="CL109" s="12">
+        <v>2884.1538461538462</v>
+      </c>
+      <c r="CM109" s="13">
+        <v>2.098051699644381</v>
+      </c>
       <c r="CN109" s="11"/>
       <c r="CO109" s="11"/>
       <c r="CP109" s="11"/>
@@ -28110,27 +29090,27 @@
       </c>
       <c r="N110" s="8">
         <f t="shared" si="20"/>
-        <v>3810603.1772727277</v>
+        <v>3835622.7208333337</v>
       </c>
       <c r="O110" s="8">
         <f t="shared" si="21"/>
-        <v>36420.272727272728</v>
+        <v>35826.916666666664</v>
       </c>
       <c r="P110" s="8">
         <f t="shared" si="22"/>
-        <v>827</v>
+        <v>908</v>
       </c>
       <c r="Q110" s="9">
         <f t="shared" si="23"/>
-        <v>152055.5076783555</v>
+        <v>152073.14752202644</v>
       </c>
       <c r="R110" s="9">
         <f t="shared" si="24"/>
-        <v>1453.2877871825876</v>
+        <v>1420.4504405286343</v>
       </c>
       <c r="S110" s="10">
         <f t="shared" si="25"/>
-        <v>1.2387751027555647</v>
+        <v>1.2250377267230732</v>
       </c>
       <c r="T110" s="11">
         <v>3668431.82</v>
@@ -28330,10 +29310,24 @@
       <c r="CG110" s="13">
         <v>1.1824108945210789</v>
       </c>
-      <c r="CJ110" s="11"/>
-      <c r="CK110" s="12"/>
-      <c r="CL110" s="12"/>
-      <c r="CM110" s="13"/>
+      <c r="CH110" s="11">
+        <v>4110837.7</v>
+      </c>
+      <c r="CI110" s="11">
+        <v>29300</v>
+      </c>
+      <c r="CJ110" s="11">
+        <v>81</v>
+      </c>
+      <c r="CK110" s="12">
+        <v>152253.24814814821</v>
+      </c>
+      <c r="CL110" s="12">
+        <v>1085.185185185185</v>
+      </c>
+      <c r="CM110" s="13">
+        <v>1.0739265903656661</v>
+      </c>
       <c r="CN110" s="11"/>
       <c r="CO110" s="11"/>
       <c r="CP110" s="11"/>
@@ -28380,27 +29374,27 @@
       </c>
       <c r="N111" s="8">
         <f t="shared" si="20"/>
-        <v>5020995.5318181822</v>
+        <v>5072110.3208333338</v>
       </c>
       <c r="O111" s="8">
         <f t="shared" si="21"/>
-        <v>56723</v>
+        <v>57265</v>
       </c>
       <c r="P111" s="8">
         <f t="shared" si="22"/>
-        <v>855</v>
+        <v>938</v>
       </c>
       <c r="Q111" s="9">
         <f t="shared" si="23"/>
-        <v>193792.81</v>
+        <v>194665.21487206823</v>
       </c>
       <c r="R111" s="9">
         <f t="shared" si="24"/>
-        <v>2189.3087719298246</v>
+        <v>2197.8038379530917</v>
       </c>
       <c r="S111" s="10">
         <f t="shared" si="25"/>
-        <v>1.3511203689560221</v>
+        <v>1.3509865269064847</v>
       </c>
       <c r="T111" s="11">
         <v>5164060.5</v>
@@ -28600,10 +29594,24 @@
       <c r="CG111" s="13">
         <v>1.367150495229962</v>
       </c>
-      <c r="CJ111" s="11"/>
-      <c r="CK111" s="12"/>
-      <c r="CL111" s="12"/>
-      <c r="CM111" s="13"/>
+      <c r="CH111" s="11">
+        <v>5634373</v>
+      </c>
+      <c r="CI111" s="11">
+        <v>63227</v>
+      </c>
+      <c r="CJ111" s="11">
+        <v>83</v>
+      </c>
+      <c r="CK111" s="12">
+        <v>203652.03614457831</v>
+      </c>
+      <c r="CL111" s="12">
+        <v>2285.3132530120479</v>
+      </c>
+      <c r="CM111" s="13">
+        <v>1.349514264361575</v>
+      </c>
       <c r="CN111" s="11"/>
       <c r="CO111" s="11"/>
       <c r="CP111" s="11"/>
@@ -28650,27 +29658,27 @@
       </c>
       <c r="N112" s="8">
         <f t="shared" si="20"/>
-        <v>6281232.1545454552</v>
+        <v>6341030.875</v>
       </c>
       <c r="O112" s="8">
         <f t="shared" si="21"/>
-        <v>52818.454545454544</v>
+        <v>52291.25</v>
       </c>
       <c r="P112" s="8">
         <f t="shared" si="22"/>
-        <v>845</v>
+        <v>925</v>
       </c>
       <c r="Q112" s="9">
         <f t="shared" si="23"/>
-        <v>245302.55751479292</v>
+        <v>246786.06648648647</v>
       </c>
       <c r="R112" s="9">
         <f t="shared" si="24"/>
-        <v>2062.7325443786981</v>
+        <v>2035.118918918919</v>
       </c>
       <c r="S112" s="10">
         <f t="shared" si="25"/>
-        <v>1.1581526754280387</v>
+        <v>1.1482471647833763</v>
       </c>
       <c r="T112" s="11">
         <v>6721992.2000000002</v>
@@ -28870,10 +29878,24 @@
       <c r="CG112" s="13">
         <v>1.0899548831862951</v>
       </c>
-      <c r="CJ112" s="11"/>
-      <c r="CK112" s="12"/>
-      <c r="CL112" s="12"/>
-      <c r="CM112" s="13"/>
+      <c r="CH112" s="11">
+        <v>6998816.7999999998</v>
+      </c>
+      <c r="CI112" s="11">
+        <v>46492</v>
+      </c>
+      <c r="CJ112" s="11">
+        <v>80</v>
+      </c>
+      <c r="CK112" s="12">
+        <v>262455.63</v>
+      </c>
+      <c r="CL112" s="12">
+        <v>1743.45</v>
+      </c>
+      <c r="CM112" s="13">
+        <v>1.0392865476920889</v>
+      </c>
       <c r="CN112" s="11"/>
       <c r="CO112" s="11"/>
       <c r="CP112" s="11"/>
@@ -28920,27 +29942,27 @@
       </c>
       <c r="N113" s="8">
         <f t="shared" si="20"/>
-        <v>5164162.8181818184</v>
+        <v>5167357.833333333</v>
       </c>
       <c r="O113" s="8">
         <f t="shared" si="21"/>
-        <v>34247.272727272728</v>
+        <v>34093.583333333336</v>
       </c>
       <c r="P113" s="8">
         <f t="shared" si="22"/>
-        <v>862</v>
+        <v>945</v>
       </c>
       <c r="Q113" s="9">
         <f t="shared" si="23"/>
-        <v>197699.96867749421</v>
+        <v>196851.72698412696</v>
       </c>
       <c r="R113" s="9">
         <f t="shared" si="24"/>
-        <v>1311.0904872389792</v>
+        <v>1298.8031746031745</v>
       </c>
       <c r="S113" s="10">
         <f t="shared" si="25"/>
-        <v>1.0365583689232147</v>
+        <v>1.0338340912502788</v>
       </c>
       <c r="T113" s="11">
         <v>5240332</v>
@@ -29140,10 +30162,24 @@
       <c r="CG113" s="13">
         <v>0.97691491262417607</v>
       </c>
-      <c r="CJ113" s="11"/>
-      <c r="CK113" s="12"/>
-      <c r="CL113" s="12"/>
-      <c r="CM113" s="13"/>
+      <c r="CH113" s="11">
+        <v>5202503</v>
+      </c>
+      <c r="CI113" s="11">
+        <v>32403</v>
+      </c>
+      <c r="CJ113" s="11">
+        <v>83</v>
+      </c>
+      <c r="CK113" s="12">
+        <v>188042.27710843369</v>
+      </c>
+      <c r="CL113" s="12">
+        <v>1171.192771084337</v>
+      </c>
+      <c r="CM113" s="13">
+        <v>1.003867036847983</v>
+      </c>
       <c r="CN113" s="11"/>
       <c r="CO113" s="11"/>
       <c r="CP113" s="11"/>
@@ -29190,27 +30226,27 @@
       </c>
       <c r="N114" s="8">
         <f t="shared" si="20"/>
-        <v>3512425.4245454548</v>
+        <v>3541045.3675000002</v>
       </c>
       <c r="O114" s="8">
         <f t="shared" si="21"/>
-        <v>21560.090909090908</v>
+        <v>21475.833333333332</v>
       </c>
       <c r="P114" s="8">
         <f t="shared" si="22"/>
-        <v>819</v>
+        <v>894</v>
       </c>
       <c r="Q114" s="9">
         <f t="shared" si="23"/>
-        <v>141526.29915750917</v>
+        <v>142592.4309060403</v>
       </c>
       <c r="R114" s="9">
         <f t="shared" si="24"/>
-        <v>868.72161172161168</v>
+        <v>864.79865771812069</v>
       </c>
       <c r="S114" s="10">
         <f t="shared" si="25"/>
-        <v>0.99810803506073453</v>
+        <v>0.99224517838527537</v>
       </c>
       <c r="T114" s="11">
         <v>3138967.83</v>
@@ -29410,10 +30446,24 @@
       <c r="CG114" s="13">
         <v>0.99133650262203965</v>
       </c>
-      <c r="CJ114" s="11"/>
-      <c r="CK114" s="12"/>
-      <c r="CL114" s="12"/>
-      <c r="CM114" s="13"/>
+      <c r="CH114" s="11">
+        <v>3855864.74</v>
+      </c>
+      <c r="CI114" s="11">
+        <v>20549</v>
+      </c>
+      <c r="CJ114" s="11">
+        <v>75</v>
+      </c>
+      <c r="CK114" s="12">
+        <v>154234.58960000001</v>
+      </c>
+      <c r="CL114" s="12">
+        <v>821.96</v>
+      </c>
+      <c r="CM114" s="13">
+        <v>0.9277537549552255</v>
+      </c>
       <c r="CN114" s="11"/>
       <c r="CO114" s="11"/>
       <c r="CP114" s="11"/>
@@ -29460,27 +30510,27 @@
       </c>
       <c r="N115" s="8">
         <f t="shared" si="20"/>
-        <v>3667482.2568181823</v>
+        <v>3804429.8837500005</v>
       </c>
       <c r="O115" s="8">
         <f t="shared" si="21"/>
-        <v>13066.90909090909</v>
+        <v>13467</v>
       </c>
       <c r="P115" s="8">
         <f t="shared" si="22"/>
-        <v>787</v>
+        <v>865</v>
       </c>
       <c r="Q115" s="9">
         <f t="shared" si="23"/>
-        <v>153782.61051461246</v>
+        <v>158334.65412138728</v>
       </c>
       <c r="R115" s="9">
         <f t="shared" si="24"/>
-        <v>547.91359593392622</v>
+        <v>560.47630057803462</v>
       </c>
       <c r="S115" s="10">
         <f t="shared" si="25"/>
-        <v>0.75136260346396955</v>
+        <v>0.75015848220089587</v>
       </c>
       <c r="T115" s="11">
         <v>3949118.67</v>
@@ -29680,10 +30730,24 @@
       <c r="CG115" s="13">
         <v>0.84773941860121704</v>
       </c>
-      <c r="CJ115" s="11"/>
-      <c r="CK115" s="12"/>
-      <c r="CL115" s="12"/>
-      <c r="CM115" s="13"/>
+      <c r="CH115" s="11">
+        <v>5310853.78</v>
+      </c>
+      <c r="CI115" s="11">
+        <v>17868</v>
+      </c>
+      <c r="CJ115" s="11">
+        <v>78</v>
+      </c>
+      <c r="CK115" s="12">
+        <v>204263.60692307691</v>
+      </c>
+      <c r="CL115" s="12">
+        <v>687.23076923076917</v>
+      </c>
+      <c r="CM115" s="13">
+        <v>0.73691314830708532</v>
+      </c>
       <c r="CN115" s="11"/>
       <c r="CO115" s="11"/>
       <c r="CP115" s="11"/>
@@ -29730,27 +30794,27 @@
       </c>
       <c r="N116" s="8">
         <f t="shared" si="20"/>
-        <v>2995571.7609130656</v>
+        <v>3032308.784821759</v>
       </c>
       <c r="O116" s="8">
         <f t="shared" si="21"/>
-        <v>25863.222222222223</v>
+        <v>25942.799999999999</v>
       </c>
       <c r="P116" s="8">
         <f t="shared" si="22"/>
-        <v>563</v>
+        <v>641</v>
       </c>
       <c r="Q116" s="9">
         <f t="shared" si="23"/>
-        <v>143659.74697096407</v>
+        <v>141917.72783877188</v>
       </c>
       <c r="R116" s="9">
         <f t="shared" si="24"/>
-        <v>1240.3321492007105</v>
+        <v>1214.1716068642745</v>
       </c>
       <c r="S116" s="10">
         <f t="shared" si="25"/>
-        <v>1.2589997588287374</v>
+        <v>1.2463143888739778</v>
       </c>
       <c r="T116" s="11">
         <v>4159158</v>
@@ -29926,10 +30990,24 @@
       <c r="CG116" s="13">
         <v>1.252069103109573</v>
       </c>
-      <c r="CJ116" s="11"/>
-      <c r="CK116" s="12"/>
-      <c r="CL116" s="12"/>
-      <c r="CM116" s="13"/>
+      <c r="CH116" s="11">
+        <v>3362942</v>
+      </c>
+      <c r="CI116" s="11">
+        <v>26659</v>
+      </c>
+      <c r="CJ116" s="11">
+        <v>78</v>
+      </c>
+      <c r="CK116" s="12">
+        <v>129343.92307692311</v>
+      </c>
+      <c r="CL116" s="12">
+        <v>1025.346153846154</v>
+      </c>
+      <c r="CM116" s="13">
+        <v>1.1321460592811401</v>
+      </c>
       <c r="CN116" s="11"/>
       <c r="CO116" s="11"/>
       <c r="CP116" s="11"/>
@@ -29976,27 +31054,27 @@
       </c>
       <c r="N117" s="8">
         <f t="shared" si="20"/>
-        <v>3184985.3128138888</v>
+        <v>3088975.1025580806</v>
       </c>
       <c r="O117" s="8">
         <f t="shared" si="21"/>
-        <v>26438.9</v>
+        <v>25652.090909090908</v>
       </c>
       <c r="P117" s="8">
         <f t="shared" si="22"/>
-        <v>629</v>
+        <v>677</v>
       </c>
       <c r="Q117" s="9">
         <f t="shared" si="23"/>
-        <v>151907.08964136196</v>
+        <v>150570.42597402754</v>
       </c>
       <c r="R117" s="9">
         <f t="shared" si="24"/>
-        <v>1260.9968203497615</v>
+        <v>1250.3973412112259</v>
       </c>
       <c r="S117" s="10">
         <f t="shared" si="25"/>
-        <v>1.1649845270614769</v>
+        <v>1.1648538664024406</v>
       </c>
       <c r="T117" s="11">
         <v>4630985</v>
@@ -30184,10 +31262,24 @@
       <c r="CG117" s="13">
         <v>1.2171055344113499</v>
       </c>
-      <c r="CJ117" s="11"/>
-      <c r="CK117" s="12"/>
-      <c r="CL117" s="12"/>
-      <c r="CM117" s="13"/>
+      <c r="CH117" s="11">
+        <v>2128873</v>
+      </c>
+      <c r="CI117" s="11">
+        <v>17784</v>
+      </c>
+      <c r="CJ117" s="11">
+        <v>48</v>
+      </c>
+      <c r="CK117" s="12">
+        <v>133054.5625</v>
+      </c>
+      <c r="CL117" s="12">
+        <v>1111.5</v>
+      </c>
+      <c r="CM117" s="13">
+        <v>1.163547259812078</v>
+      </c>
       <c r="CN117" s="11"/>
       <c r="CO117" s="11"/>
       <c r="CP117" s="11"/>
@@ -30468,27 +31560,27 @@
       </c>
       <c r="N119" s="8">
         <f t="shared" si="20"/>
-        <v>3855702.81</v>
+        <v>3903793.6454545455</v>
       </c>
       <c r="O119" s="8">
         <f t="shared" si="21"/>
-        <v>26526.5</v>
+        <v>27462.090909090908</v>
       </c>
       <c r="P119" s="8">
         <f t="shared" si="22"/>
-        <v>638</v>
+        <v>719</v>
       </c>
       <c r="Q119" s="9">
         <f t="shared" si="23"/>
-        <v>181302.63996865205</v>
+        <v>179172.7264255911</v>
       </c>
       <c r="R119" s="9">
         <f t="shared" si="24"/>
-        <v>1247.3275862068965</v>
+        <v>1260.4297635605008</v>
       </c>
       <c r="S119" s="10">
         <f t="shared" si="25"/>
-        <v>1.0340400095991487</v>
+        <v>1.0460828273174907</v>
       </c>
       <c r="T119" s="11">
         <v>4875456.92</v>
@@ -30676,10 +31768,24 @@
       <c r="CG119" s="13">
         <v>1.181670018598967</v>
       </c>
-      <c r="CJ119" s="11"/>
-      <c r="CK119" s="12"/>
-      <c r="CL119" s="12"/>
-      <c r="CM119" s="13"/>
+      <c r="CH119" s="11">
+        <v>4384702</v>
+      </c>
+      <c r="CI119" s="11">
+        <v>36818</v>
+      </c>
+      <c r="CJ119" s="11">
+        <v>81</v>
+      </c>
+      <c r="CK119" s="12">
+        <v>162396.37037037039</v>
+      </c>
+      <c r="CL119" s="12">
+        <v>1363.62962962963</v>
+      </c>
+      <c r="CM119" s="13">
+        <v>1.1665110045009091</v>
+      </c>
       <c r="CN119" s="11"/>
       <c r="CO119" s="11"/>
       <c r="CP119" s="11"/>
@@ -30726,27 +31832,27 @@
       </c>
       <c r="N120" s="8">
         <f t="shared" si="20"/>
-        <v>5256924.9727272727</v>
+        <v>5256875.3916666666</v>
       </c>
       <c r="O120" s="8">
         <f t="shared" si="21"/>
-        <v>27748.363636363636</v>
+        <v>27756.666666666668</v>
       </c>
       <c r="P120" s="8">
         <f t="shared" si="22"/>
-        <v>848</v>
+        <v>928</v>
       </c>
       <c r="Q120" s="9">
         <f t="shared" si="23"/>
-        <v>204573.73125000001</v>
+        <v>203930.51088362068</v>
       </c>
       <c r="R120" s="9">
         <f t="shared" si="24"/>
-        <v>1079.8301886792451</v>
+        <v>1076.7672413793102</v>
       </c>
       <c r="S120" s="10">
         <f t="shared" si="25"/>
-        <v>0.91887910959177643</v>
+        <v>0.91926032482332232</v>
       </c>
       <c r="T120" s="11">
         <v>5796465.7000000002</v>
@@ -30946,10 +32052,24 @@
       <c r="CG120" s="13">
         <v>0.98803629124724013</v>
       </c>
-      <c r="CJ120" s="11"/>
-      <c r="CK120" s="12"/>
-      <c r="CL120" s="12"/>
-      <c r="CM120" s="13"/>
+      <c r="CH120" s="11">
+        <v>5256330</v>
+      </c>
+      <c r="CI120" s="11">
+        <v>27848</v>
+      </c>
+      <c r="CJ120" s="11">
+        <v>80</v>
+      </c>
+      <c r="CK120" s="12">
+        <v>197112.375</v>
+      </c>
+      <c r="CL120" s="12">
+        <v>1044.3</v>
+      </c>
+      <c r="CM120" s="13">
+        <v>0.92345369237032615</v>
+      </c>
       <c r="CN120" s="11"/>
       <c r="CO120" s="11"/>
       <c r="CP120" s="11"/>
@@ -30996,27 +32116,27 @@
       </c>
       <c r="N121" s="8">
         <f t="shared" si="20"/>
-        <v>5400939.1727272728</v>
+        <v>5400724.0499999998</v>
       </c>
       <c r="O121" s="8">
         <f t="shared" si="21"/>
-        <v>40390.545454545456</v>
+        <v>39960.416666666664</v>
       </c>
       <c r="P121" s="8">
         <f t="shared" si="22"/>
-        <v>852</v>
+        <v>934</v>
       </c>
       <c r="Q121" s="9">
         <f t="shared" si="23"/>
-        <v>209191.3059859155</v>
+        <v>208164.95267665954</v>
       </c>
       <c r="R121" s="9">
         <f t="shared" si="24"/>
-        <v>1564.4225352112676</v>
+        <v>1540.230192719486</v>
       </c>
       <c r="S121" s="10">
         <f t="shared" si="25"/>
-        <v>1.0988995636470746</v>
+        <v>1.0929194762728791</v>
       </c>
       <c r="T121" s="11">
         <v>5298868.4000000004</v>
@@ -31216,10 +32336,24 @@
       <c r="CG121" s="13">
         <v>1.0629943316753669</v>
       </c>
-      <c r="CJ121" s="11"/>
-      <c r="CK121" s="12"/>
-      <c r="CL121" s="12"/>
-      <c r="CM121" s="13"/>
+      <c r="CH121" s="11">
+        <v>5398357.7000000002</v>
+      </c>
+      <c r="CI121" s="11">
+        <v>35229</v>
+      </c>
+      <c r="CJ121" s="11">
+        <v>82</v>
+      </c>
+      <c r="CK121" s="12">
+        <v>197500.89146341459</v>
+      </c>
+      <c r="CL121" s="12">
+        <v>1288.8658536585369</v>
+      </c>
+      <c r="CM121" s="13">
+        <v>1.0271385151567289</v>
+      </c>
       <c r="CN121" s="11"/>
       <c r="CO121" s="11"/>
       <c r="CP121" s="11"/>
@@ -31266,27 +32400,27 @@
       </c>
       <c r="N122" s="8">
         <f t="shared" si="20"/>
-        <v>4629534.5454545459</v>
+        <v>4682753.583333333</v>
       </c>
       <c r="O122" s="8">
         <f t="shared" si="21"/>
-        <v>23416.636363636364</v>
+        <v>23612.333333333332</v>
       </c>
       <c r="P122" s="8">
         <f t="shared" si="22"/>
-        <v>852</v>
+        <v>937</v>
       </c>
       <c r="Q122" s="9">
         <f t="shared" si="23"/>
-        <v>179312.95774647887</v>
+        <v>179913.69156883672</v>
       </c>
       <c r="R122" s="9">
         <f t="shared" si="24"/>
-        <v>906.98239436619724</v>
+        <v>907.19743863393819</v>
       </c>
       <c r="S122" s="10">
         <f t="shared" si="25"/>
-        <v>0.90635086921355523</v>
+        <v>0.90489544415000978</v>
       </c>
       <c r="T122" s="11">
         <v>4349659</v>
@@ -31486,10 +32620,24 @@
       <c r="CG122" s="13">
         <v>0.97932376384640329</v>
       </c>
-      <c r="CJ122" s="11"/>
-      <c r="CK122" s="12"/>
-      <c r="CL122" s="12"/>
-      <c r="CM122" s="13"/>
+      <c r="CH122" s="11">
+        <v>5268163</v>
+      </c>
+      <c r="CI122" s="11">
+        <v>25765</v>
+      </c>
+      <c r="CJ122" s="11">
+        <v>85</v>
+      </c>
+      <c r="CK122" s="12">
+        <v>185935.16470588229</v>
+      </c>
+      <c r="CL122" s="12">
+        <v>909.35294117647061</v>
+      </c>
+      <c r="CM122" s="13">
+        <v>0.88888576845100908</v>
+      </c>
       <c r="CN122" s="11"/>
       <c r="CO122" s="11"/>
       <c r="CP122" s="11"/>
@@ -31536,27 +32684,27 @@
       </c>
       <c r="N123" s="8">
         <f t="shared" si="20"/>
-        <v>2844949.8022727272</v>
+        <v>2866958.6520833336</v>
       </c>
       <c r="O123" s="8">
         <f t="shared" si="21"/>
-        <v>79199.727272727279</v>
+        <v>78870.083333333328</v>
       </c>
       <c r="P123" s="8">
         <f t="shared" si="22"/>
-        <v>839</v>
+        <v>920</v>
       </c>
       <c r="Q123" s="9">
         <f t="shared" si="23"/>
-        <v>111899.09830154946</v>
+        <v>112185.33855978261</v>
       </c>
       <c r="R123" s="9">
         <f t="shared" si="24"/>
-        <v>3115.1263408820023</v>
+        <v>3086.2206521739135</v>
       </c>
       <c r="S123" s="10">
         <f t="shared" si="25"/>
-        <v>2.1392542920656954</v>
+        <v>2.1259481468889043</v>
       </c>
       <c r="T123" s="11">
         <v>3151591.55</v>
@@ -31756,10 +32904,24 @@
       <c r="CG123" s="13">
         <v>2.126482302997784</v>
       </c>
-      <c r="CJ123" s="11"/>
-      <c r="CK123" s="12"/>
-      <c r="CL123" s="12"/>
-      <c r="CM123" s="13"/>
+      <c r="CH123" s="11">
+        <v>3109056</v>
+      </c>
+      <c r="CI123" s="11">
+        <v>75244</v>
+      </c>
+      <c r="CJ123" s="11">
+        <v>81</v>
+      </c>
+      <c r="CK123" s="12">
+        <v>115150.2222222222</v>
+      </c>
+      <c r="CL123" s="12">
+        <v>2786.8148148148148</v>
+      </c>
+      <c r="CM123" s="13">
+        <v>1.9795805499442041</v>
+      </c>
       <c r="CN123" s="11"/>
       <c r="CO123" s="11"/>
       <c r="CP123" s="11"/>
@@ -31806,27 +32968,27 @@
       </c>
       <c r="N124" s="8">
         <f t="shared" si="20"/>
-        <v>311243.32272727269</v>
+        <v>317427.42916666664</v>
       </c>
       <c r="O124" s="8">
         <f t="shared" si="21"/>
-        <v>119540</v>
+        <v>121073</v>
       </c>
       <c r="P124" s="8">
         <f t="shared" si="22"/>
-        <v>736</v>
+        <v>808</v>
       </c>
       <c r="Q124" s="9">
         <f t="shared" si="23"/>
-        <v>13955.203328804346</v>
+        <v>14142.806250000001</v>
       </c>
       <c r="R124" s="9">
         <f t="shared" si="24"/>
-        <v>5359.809782608696</v>
+        <v>5394.3415841584156</v>
       </c>
       <c r="S124" s="10">
         <f t="shared" si="25"/>
-        <v>8.2315261138613192</v>
+        <v>8.1804626081408731</v>
       </c>
       <c r="T124" s="11">
         <v>415887.2</v>
@@ -32026,10 +33188,24 @@
       <c r="CG124" s="13">
         <v>7.624950335860718</v>
       </c>
-      <c r="CJ124" s="11"/>
-      <c r="CK124" s="12"/>
-      <c r="CL124" s="12"/>
-      <c r="CM124" s="13"/>
+      <c r="CH124" s="11">
+        <v>385452.6</v>
+      </c>
+      <c r="CI124" s="11">
+        <v>137936</v>
+      </c>
+      <c r="CJ124" s="11">
+        <v>72</v>
+      </c>
+      <c r="CK124" s="12">
+        <v>16060.525</v>
+      </c>
+      <c r="CL124" s="12">
+        <v>5747.3333333333339</v>
+      </c>
+      <c r="CM124" s="13">
+        <v>7.6187640452159506</v>
+      </c>
       <c r="CN124" s="11"/>
       <c r="CO124" s="11"/>
       <c r="CP124" s="11"/>
@@ -32064,27 +33240,27 @@
       </c>
       <c r="N125" s="8">
         <f t="shared" si="20"/>
-        <v>3708638.1436363626</v>
+        <v>3775757.773333333</v>
       </c>
       <c r="O125" s="8">
         <f t="shared" si="21"/>
-        <v>5925.545454545455</v>
+        <v>6006.833333333333</v>
       </c>
       <c r="P125" s="8">
         <f t="shared" si="22"/>
-        <v>697</v>
+        <v>759</v>
       </c>
       <c r="Q125" s="9">
         <f t="shared" si="23"/>
-        <v>175588.31956958389</v>
+        <v>179087.32521739128</v>
       </c>
       <c r="R125" s="9">
         <f t="shared" si="24"/>
-        <v>280.54949784791967</v>
+        <v>284.90909090909088</v>
       </c>
       <c r="S125" s="10">
         <f t="shared" si="25"/>
-        <v>0.47200465593111912</v>
+        <v>0.47382278004966544</v>
       </c>
       <c r="T125" s="11">
         <v>3715308.76</v>
@@ -32284,10 +33460,24 @@
       <c r="CG125" s="13">
         <v>0.61594877141061322</v>
       </c>
-      <c r="CJ125" s="11"/>
-      <c r="CK125" s="12"/>
-      <c r="CL125" s="12"/>
-      <c r="CM125" s="13"/>
+      <c r="CH125" s="11">
+        <v>4514073.7</v>
+      </c>
+      <c r="CI125" s="11">
+        <v>6901</v>
+      </c>
+      <c r="CJ125" s="11">
+        <v>62</v>
+      </c>
+      <c r="CK125" s="12">
+        <v>218422.9209677419</v>
+      </c>
+      <c r="CL125" s="12">
+        <v>333.91935483870969</v>
+      </c>
+      <c r="CM125" s="13">
+        <v>0.49382214535367502</v>
+      </c>
       <c r="CN125" s="11"/>
       <c r="CO125" s="11"/>
       <c r="CP125" s="11"/>
@@ -32322,27 +33512,27 @@
       </c>
       <c r="N126" s="8">
         <f t="shared" si="20"/>
-        <v>3532672.6009090911</v>
+        <v>3582075.2925</v>
       </c>
       <c r="O126" s="8">
         <f t="shared" si="21"/>
-        <v>5680.636363636364</v>
+        <v>5783.833333333333</v>
       </c>
       <c r="P126" s="8">
         <f t="shared" si="22"/>
-        <v>744</v>
+        <v>808</v>
       </c>
       <c r="Q126" s="9">
         <f t="shared" si="23"/>
-        <v>156691.12342741934</v>
+        <v>159597.41402227723</v>
       </c>
       <c r="R126" s="9">
         <f t="shared" si="24"/>
-        <v>251.96370967741933</v>
+        <v>257.69554455445541</v>
       </c>
       <c r="S126" s="10">
         <f t="shared" si="25"/>
-        <v>0.48761748111089226</v>
+        <v>0.49022641353636748</v>
       </c>
       <c r="T126" s="11">
         <v>3223771.74</v>
@@ -32542,10 +33732,24 @@
       <c r="CG126" s="13">
         <v>0.60823435733604014</v>
       </c>
-      <c r="CJ126" s="11"/>
-      <c r="CK126" s="12"/>
-      <c r="CL126" s="12"/>
-      <c r="CM126" s="13"/>
+      <c r="CH126" s="11">
+        <v>4125504.9</v>
+      </c>
+      <c r="CI126" s="11">
+        <v>6919</v>
+      </c>
+      <c r="CJ126" s="11">
+        <v>64</v>
+      </c>
+      <c r="CK126" s="12">
+        <v>193383.04218749999</v>
+      </c>
+      <c r="CL126" s="12">
+        <v>324.328125</v>
+      </c>
+      <c r="CM126" s="13">
+        <v>0.5189246702165955</v>
+      </c>
       <c r="CN126" s="11"/>
       <c r="CO126" s="11"/>
       <c r="CP126" s="11"/>
@@ -32580,27 +33784,27 @@
       </c>
       <c r="N127" s="8">
         <f t="shared" si="20"/>
-        <v>9508803.1863636374</v>
+        <v>9416514.8416666668</v>
       </c>
       <c r="O127" s="8">
         <f t="shared" si="21"/>
-        <v>181035.45454545456</v>
+        <v>181178.25</v>
       </c>
       <c r="P127" s="8">
         <f t="shared" si="22"/>
-        <v>781</v>
+        <v>853</v>
       </c>
       <c r="Q127" s="9">
         <f t="shared" si="23"/>
-        <v>401780.4163252241</v>
+        <v>397414.45990621339</v>
       </c>
       <c r="R127" s="9">
         <f t="shared" si="24"/>
-        <v>7649.3854033290645</v>
+        <v>7646.444314185228</v>
       </c>
       <c r="S127" s="10">
         <f t="shared" si="25"/>
-        <v>1.7566421972566155</v>
+        <v>1.7665788504561082</v>
       </c>
       <c r="T127" s="11">
         <v>9039184.5999999996</v>
@@ -32800,10 +34004,24 @@
       <c r="CG127" s="13">
         <v>1.782470399260657</v>
       </c>
-      <c r="CJ127" s="11"/>
-      <c r="CK127" s="12"/>
-      <c r="CL127" s="12"/>
-      <c r="CM127" s="13"/>
+      <c r="CH127" s="11">
+        <v>8401343.0500000007</v>
+      </c>
+      <c r="CI127" s="11">
+        <v>182749</v>
+      </c>
+      <c r="CJ127" s="11">
+        <v>72</v>
+      </c>
+      <c r="CK127" s="12">
+        <v>350055.9604166667</v>
+      </c>
+      <c r="CL127" s="12">
+        <v>7614.541666666667</v>
+      </c>
+      <c r="CM127" s="13">
+        <v>1.8758820356505259</v>
+      </c>
       <c r="CN127" s="11"/>
       <c r="CO127" s="11"/>
       <c r="CP127" s="11"/>
@@ -32838,27 +34056,27 @@
       </c>
       <c r="N128" s="8">
         <f t="shared" si="20"/>
-        <v>4190628.709090909</v>
+        <v>4162342.5666666664</v>
       </c>
       <c r="O128" s="8">
         <f t="shared" si="21"/>
-        <v>243425.90909090909</v>
+        <v>237230.75</v>
       </c>
       <c r="P128" s="8">
         <f t="shared" si="22"/>
-        <v>782</v>
+        <v>853</v>
       </c>
       <c r="Q128" s="9">
         <f t="shared" si="23"/>
-        <v>176842.38797953964</v>
+        <v>175667.44712778428</v>
       </c>
       <c r="R128" s="9">
         <f t="shared" si="24"/>
-        <v>10272.44884910486</v>
+        <v>10012.083235638922</v>
       </c>
       <c r="S128" s="10">
         <f t="shared" si="25"/>
-        <v>3.050238034147712</v>
+        <v>3.0183630520989713</v>
       </c>
       <c r="T128" s="11">
         <v>4043082</v>
@@ -33058,10 +34276,24 @@
       <c r="CG128" s="13">
         <v>2.9721297829259949</v>
       </c>
-      <c r="CJ128" s="11"/>
-      <c r="CK128" s="12"/>
-      <c r="CL128" s="12"/>
-      <c r="CM128" s="13"/>
+      <c r="CH128" s="11">
+        <v>3851195</v>
+      </c>
+      <c r="CI128" s="11">
+        <v>169084</v>
+      </c>
+      <c r="CJ128" s="11">
+        <v>71</v>
+      </c>
+      <c r="CK128" s="12">
+        <v>162726.54929577469</v>
+      </c>
+      <c r="CL128" s="12">
+        <v>7144.3943661971834</v>
+      </c>
+      <c r="CM128" s="13">
+        <v>2.667738249562825</v>
+      </c>
       <c r="CN128" s="11"/>
       <c r="CO128" s="11"/>
       <c r="CP128" s="11"/>
@@ -33096,27 +34328,27 @@
       </c>
       <c r="N129" s="8">
         <f t="shared" si="20"/>
-        <v>4398590.7954545459</v>
+        <v>4395512.395833333</v>
       </c>
       <c r="O129" s="8">
         <f t="shared" si="21"/>
-        <v>229139.45454545456</v>
+        <v>225841.16666666666</v>
       </c>
       <c r="P129" s="8">
         <f t="shared" si="22"/>
-        <v>796</v>
+        <v>867</v>
       </c>
       <c r="Q129" s="9">
         <f t="shared" si="23"/>
-        <v>182353.63850502513</v>
+        <v>182512.62543252594</v>
       </c>
       <c r="R129" s="9">
         <f t="shared" si="24"/>
-        <v>9499.5</v>
+        <v>9377.4878892733559</v>
       </c>
       <c r="S129" s="10">
         <f t="shared" si="25"/>
-        <v>2.9218223664206748</v>
+        <v>2.899582721280046</v>
       </c>
       <c r="T129" s="11">
         <v>4823246</v>
@@ -33316,10 +34548,24 @@
       <c r="CG129" s="13">
         <v>3.162141418795906</v>
       </c>
-      <c r="CJ129" s="11"/>
-      <c r="CK129" s="12"/>
-      <c r="CL129" s="12"/>
-      <c r="CM129" s="13"/>
+      <c r="CH129" s="11">
+        <v>4361650</v>
+      </c>
+      <c r="CI129" s="11">
+        <v>189560</v>
+      </c>
+      <c r="CJ129" s="11">
+        <v>71</v>
+      </c>
+      <c r="CK129" s="12">
+        <v>184295.07042253521</v>
+      </c>
+      <c r="CL129" s="12">
+        <v>8009.577464788732</v>
+      </c>
+      <c r="CM129" s="13">
+        <v>2.654946624733125</v>
+      </c>
       <c r="CN129" s="11"/>
       <c r="CO129" s="11"/>
       <c r="CP129" s="11"/>
@@ -33354,27 +34600,27 @@
       </c>
       <c r="N130" s="8">
         <f t="shared" si="20"/>
-        <v>1779783.2727272727</v>
+        <v>1789336</v>
       </c>
       <c r="O130" s="8">
         <f t="shared" si="21"/>
-        <v>201000</v>
+        <v>201179.16666666666</v>
       </c>
       <c r="P130" s="8">
         <f t="shared" si="22"/>
-        <v>519</v>
+        <v>560</v>
       </c>
       <c r="Q130" s="9">
         <f t="shared" si="23"/>
-        <v>113165.41040462427</v>
+        <v>115028.74285714286</v>
       </c>
       <c r="R130" s="9">
         <f t="shared" si="24"/>
-        <v>12780.346820809249</v>
+        <v>12932.946428571429</v>
       </c>
       <c r="S130" s="10">
         <f t="shared" si="25"/>
-        <v>4.2813752301671988</v>
+        <v>4.2720589045115132</v>
       </c>
       <c r="T130" s="11">
         <v>1830116</v>
@@ -33574,10 +34820,24 @@
       <c r="CG130" s="13">
         <v>4.2467471989794596</v>
       </c>
-      <c r="CJ130" s="11"/>
-      <c r="CK130" s="12"/>
-      <c r="CL130" s="12"/>
-      <c r="CM130" s="13"/>
+      <c r="CH130" s="11">
+        <v>1894416</v>
+      </c>
+      <c r="CI130" s="11">
+        <v>203150</v>
+      </c>
+      <c r="CJ130" s="11">
+        <v>41</v>
+      </c>
+      <c r="CK130" s="12">
+        <v>138615.8048780488</v>
+      </c>
+      <c r="CL130" s="12">
+        <v>14864.634146341459</v>
+      </c>
+      <c r="CM130" s="13">
+        <v>4.1695793222989774</v>
+      </c>
       <c r="CN130" s="11"/>
       <c r="CO130" s="11"/>
       <c r="CP130" s="11"/>
@@ -33612,27 +34872,27 @@
       </c>
       <c r="N131" s="8">
         <f t="shared" si="20"/>
-        <v>717311.36363636365</v>
+        <v>730838</v>
       </c>
       <c r="O131" s="8">
         <f t="shared" si="21"/>
-        <v>172090</v>
+        <v>173480.83333333334</v>
       </c>
       <c r="P131" s="8">
         <f t="shared" si="22"/>
-        <v>514</v>
+        <v>562</v>
       </c>
       <c r="Q131" s="9">
         <f t="shared" ref="Q131:Q132" si="26">IFERROR(SUM(T131,Z131,AF131,AL131,AR131,AX131,BD131,BJ131,BP131,BV131,CB131,CH131)/P131*3," ")</f>
-        <v>46053.06420233463</v>
+        <v>46815.245551601423</v>
       </c>
       <c r="R131" s="9">
         <f t="shared" si="24"/>
-        <v>11048.579766536965</v>
+        <v>11112.651245551602</v>
       </c>
       <c r="S131" s="10">
         <f t="shared" si="25"/>
-        <v>6.3327980836301556</v>
+        <v>6.2970181410174346</v>
       </c>
       <c r="T131" s="11">
         <v>658205</v>
@@ -33832,10 +35092,24 @@
       <c r="CG131" s="13">
         <v>5.2688802688836196</v>
       </c>
-      <c r="CJ131" s="11"/>
-      <c r="CK131" s="12"/>
-      <c r="CL131" s="12"/>
-      <c r="CM131" s="13"/>
+      <c r="CH131" s="11">
+        <v>879631</v>
+      </c>
+      <c r="CI131" s="11">
+        <v>188780</v>
+      </c>
+      <c r="CJ131" s="11">
+        <v>48</v>
+      </c>
+      <c r="CK131" s="12">
+        <v>54976.9375</v>
+      </c>
+      <c r="CL131" s="12">
+        <v>11798.75</v>
+      </c>
+      <c r="CM131" s="13">
+        <v>5.9034387722774966</v>
+      </c>
       <c r="CN131" s="11"/>
       <c r="CO131" s="11"/>
       <c r="CP131" s="11"/>
@@ -33870,27 +35144,27 @@
       </c>
       <c r="N132" s="8">
         <f t="shared" si="20"/>
-        <v>4540055.4545454541</v>
+        <v>4636990.25</v>
       </c>
       <c r="O132" s="8">
         <f t="shared" si="21"/>
-        <v>23360.545454545456</v>
+        <v>23833.916666666668</v>
       </c>
       <c r="P132" s="8">
         <f t="shared" si="22"/>
-        <v>789</v>
+        <v>867</v>
       </c>
       <c r="Q132" s="9">
         <f t="shared" si="26"/>
-        <v>189888.25095057033</v>
+        <v>192539.38754325261</v>
       </c>
       <c r="R132" s="9">
         <f t="shared" si="24"/>
-        <v>977.05703422053227</v>
+        <v>989.64359861591697</v>
       </c>
       <c r="S132" s="10">
         <f t="shared" si="25"/>
-        <v>0.90663176367714304</v>
+        <v>0.90660917921656958</v>
       </c>
       <c r="T132" s="11">
         <v>5174735</v>
@@ -34090,10 +35364,24 @@
       <c r="CG132" s="13">
         <v>0.83119948831014867</v>
       </c>
-      <c r="CJ132" s="11"/>
-      <c r="CK132" s="12"/>
-      <c r="CL132" s="12"/>
-      <c r="CM132" s="13"/>
+      <c r="CH132" s="11">
+        <v>5703273</v>
+      </c>
+      <c r="CI132" s="11">
+        <v>29041</v>
+      </c>
+      <c r="CJ132" s="11">
+        <v>78</v>
+      </c>
+      <c r="CK132" s="12">
+        <v>219356.65384615379</v>
+      </c>
+      <c r="CL132" s="12">
+        <v>1116.961538461539</v>
+      </c>
+      <c r="CM132" s="13">
+        <v>0.90636075015026207</v>
+      </c>
       <c r="CN132" s="11"/>
       <c r="CO132" s="11"/>
       <c r="CP132" s="11"/>
@@ -34126,11 +35414,11 @@
       <c r="M133" s="22"/>
       <c r="N133" s="14">
         <f>SUM(N67:N132)</f>
-        <v>226417697.04982933</v>
+        <v>229075782.07099155</v>
       </c>
       <c r="O133" s="14">
         <f t="shared" ref="O133" si="28">SUM(O67:O132)</f>
-        <v>3161790.0669191922</v>
+        <v>3162846.7234848482</v>
       </c>
       <c r="P133" s="14"/>
       <c r="Q133" s="14"/>
@@ -34270,11 +35558,11 @@
       <c r="CG133" s="24"/>
       <c r="CH133" s="14">
         <f>SUM(CH67:CH132)</f>
-        <v>0</v>
+        <v>229810013.19499999</v>
       </c>
       <c r="CI133" s="14">
         <f>SUM(CI67:CI132)</f>
-        <v>0</v>
+        <v>3025367</v>
       </c>
       <c r="CJ133" s="14"/>
       <c r="CK133" s="14"/>
@@ -34740,27 +36028,27 @@
       </c>
       <c r="N137" s="8">
         <f t="shared" ref="N137:O139" si="29">IFERROR(AVERAGE(T137,Z137,AF137,AL137,AR137,AX137,BD137,BJ137,BP137,BV137,CB137,CH137)," ")</f>
-        <v>2860810.4545454546</v>
+        <v>2933686.8333333335</v>
       </c>
       <c r="O137" s="8">
         <f t="shared" si="29"/>
-        <v>421466.45454545453</v>
+        <v>431936.91666666669</v>
       </c>
       <c r="P137" s="8">
         <f>IFERROR(SUM(V137,AB137,AH137,AN137,AT137,AZ137,BF137,BL137,BR137,BX137,CD137,CJ137)," ")</f>
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="Q137" s="9">
         <f>IFERROR(SUM(T137,Z137,AF137,AL137,AR137,AX137,BD137,BJ137,BP137,BV137,CB137,CH137)/P137*3," ")</f>
-        <v>268200.98011363635</v>
+        <v>268734.67175572517</v>
       </c>
       <c r="R137" s="9">
         <f>IFERROR(SUM(U137,AA137,AG137,AM137,AS137,AY137,BE137,BK137,BQ137,BW137,CC137,CI137)/P137*3," ")</f>
-        <v>39512.48011363636</v>
+        <v>39566.740458015265</v>
       </c>
       <c r="S137" s="10">
         <f>IFERROR(AVERAGE(Y137,AE137,AK137,AQ137,AW137,BC137,BI137,BO137,BU137,CA137,CG137,CM137)," ")</f>
-        <v>4.8975193244659811</v>
+        <v>4.8954616729076248</v>
       </c>
       <c r="T137" s="11">
         <v>3567416</v>
@@ -34960,10 +36248,24 @@
       <c r="CG137" s="13">
         <v>5.0691139666453902</v>
       </c>
-      <c r="CJ137" s="11"/>
-      <c r="CK137" s="12"/>
-      <c r="CL137" s="12"/>
-      <c r="CM137" s="13"/>
+      <c r="CH137" s="11">
+        <v>3735327</v>
+      </c>
+      <c r="CI137" s="11">
+        <v>547112</v>
+      </c>
+      <c r="CJ137" s="11">
+        <v>41</v>
+      </c>
+      <c r="CK137" s="12">
+        <v>273316.60975609749</v>
+      </c>
+      <c r="CL137" s="12">
+        <v>40032.585365853658</v>
+      </c>
+      <c r="CM137" s="13">
+        <v>4.8728275057657058</v>
+      </c>
       <c r="CN137" s="11"/>
     </row>
     <row r="138" spans="1:94" x14ac:dyDescent="0.25">
@@ -35008,27 +36310,27 @@
       </c>
       <c r="N138" s="8">
         <f t="shared" si="29"/>
-        <v>2920610.0909090908</v>
+        <v>2985959.6666666665</v>
       </c>
       <c r="O138" s="8">
         <f t="shared" si="29"/>
-        <v>432607.72727272729</v>
+        <v>441200.91666666669</v>
       </c>
       <c r="P138" s="8">
         <f>IFERROR(SUM(V138,AB138,AH138,AN138,AT138,AZ138,BF138,BL138,BR138,BX138,CD138,CJ138)," ")</f>
-        <v>345</v>
+        <v>387</v>
       </c>
       <c r="Q138" s="9">
         <f>IFERROR(SUM(T138,Z138,AF138,AL138,AR138,AX138,BD138,BJ138,BP138,BV138,CB138,CH138)/P138*3," ")</f>
-        <v>279362.70434782607</v>
+        <v>277763.68992248061</v>
       </c>
       <c r="R138" s="9">
         <f>IFERROR(SUM(U138,AA138,AG138,AM138,AS138,AY138,BE138,BK138,BQ138,BW138,CC138,CI138)/P138*3," ")</f>
-        <v>41379.869565217392</v>
+        <v>41041.945736434107</v>
       </c>
       <c r="S138" s="10">
         <f>IFERROR(AVERAGE(Y138,AE138,AK138,AQ138,AW138,BC138,BI138,BO138,BU138,CA138,CG138,CM138)," ")</f>
-        <v>4.8967165274776905</v>
+        <v>4.8921259428661426</v>
       </c>
       <c r="T138" s="11">
         <v>1713754</v>
@@ -35228,10 +36530,24 @@
       <c r="CG138" s="13">
         <v>5.074471429440738</v>
       </c>
-      <c r="CJ138" s="11"/>
-      <c r="CK138" s="12"/>
-      <c r="CL138" s="12"/>
-      <c r="CM138" s="13"/>
+      <c r="CH138" s="11">
+        <v>3704805</v>
+      </c>
+      <c r="CI138" s="11">
+        <v>535726</v>
+      </c>
+      <c r="CJ138" s="11">
+        <v>42</v>
+      </c>
+      <c r="CK138" s="12">
+        <v>264628.92857142858</v>
+      </c>
+      <c r="CL138" s="12">
+        <v>38266.142857142862</v>
+      </c>
+      <c r="CM138" s="13">
+        <v>4.8416295121391144</v>
+      </c>
     </row>
     <row r="139" spans="1:94" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
@@ -35275,27 +36591,27 @@
       </c>
       <c r="N139" s="8">
         <f t="shared" si="29"/>
-        <v>814799.63636363635</v>
+        <v>835120.91666666663</v>
       </c>
       <c r="O139" s="8">
         <f t="shared" si="29"/>
-        <v>860900.90909090906</v>
+        <v>882924.5</v>
       </c>
       <c r="P139" s="8">
         <f>IFERROR(SUM(V139,AB139,AH139,AN139,AT139,AZ139,BF139,BL139,BR139,BX139,CD139,CJ139)," ")</f>
-        <v>359</v>
+        <v>400</v>
       </c>
       <c r="Q139" s="9">
         <f>IFERROR(SUM(T139,Z139,AF139,AL139,AR139,AX139,BD139,BJ139,BP139,BV139,CB139,CH139)/P139*3," ")</f>
-        <v>74898.016713091929</v>
+        <v>75160.882499999992</v>
       </c>
       <c r="R139" s="9">
         <f>IFERROR(SUM(U139,AA139,AG139,AM139,AS139,AY139,BE139,BK139,BQ139,BW139,CC139,CI139)/P139*3," ")</f>
-        <v>79135.738161559886</v>
+        <v>79463.205000000002</v>
       </c>
       <c r="S139" s="10">
         <f>IFERROR(AVERAGE(Y139,AE139,AK139,AQ139,AW139,BC139,BI139,BO139,BU139,CA139,CG139,CM139)," ")</f>
-        <v>14.70977001838321</v>
+        <v>14.699129727073183</v>
       </c>
       <c r="T139" s="11">
         <v>670174</v>
@@ -35495,10 +36811,24 @@
       <c r="CG139" s="13">
         <v>15.23817300243749</v>
       </c>
-      <c r="CJ139" s="11"/>
-      <c r="CK139" s="12"/>
-      <c r="CL139" s="12"/>
-      <c r="CM139" s="13"/>
+      <c r="CH139" s="11">
+        <v>1058655</v>
+      </c>
+      <c r="CI139" s="11">
+        <v>1125184</v>
+      </c>
+      <c r="CJ139" s="11">
+        <v>41</v>
+      </c>
+      <c r="CK139" s="12">
+        <v>77462.560975609755</v>
+      </c>
+      <c r="CL139" s="12">
+        <v>82330.536585365859</v>
+      </c>
+      <c r="CM139" s="13">
+        <v>14.58208652266287</v>
+      </c>
     </row>
     <row r="140" spans="1:94" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
@@ -35528,11 +36858,11 @@
       <c r="M140" s="22"/>
       <c r="N140" s="14">
         <f>SUM(N137:N139)</f>
-        <v>6596220.1818181816</v>
+        <v>6754767.416666667</v>
       </c>
       <c r="O140" s="14">
         <f>SUM(O137:O139)</f>
-        <v>1714975.0909090908</v>
+        <v>1756062.3333333335</v>
       </c>
       <c r="P140" s="14"/>
       <c r="Q140" s="14"/>
@@ -35672,11 +37002,11 @@
       <c r="CG140" s="14"/>
       <c r="CH140" s="14">
         <f>SUM(CH137:CH139)</f>
-        <v>0</v>
+        <v>8498787</v>
       </c>
       <c r="CI140" s="14">
         <f>SUM(CI137:CI139)</f>
-        <v>0</v>
+        <v>2208022</v>
       </c>
       <c r="CJ140" s="14"/>
       <c r="CK140" s="14"/>
@@ -35698,6 +37028,35 @@
   </sheetData>
   <autoFilter ref="A2:CM63" xr:uid="{B264AC42-3408-4CC4-A254-80BEFA0AA9F5}"/>
   <mergeCells count="45">
+    <mergeCell ref="CB135:CG135"/>
+    <mergeCell ref="CH135:CM135"/>
+    <mergeCell ref="N135:S135"/>
+    <mergeCell ref="AX135:BC135"/>
+    <mergeCell ref="BD135:BI135"/>
+    <mergeCell ref="BJ135:BO135"/>
+    <mergeCell ref="BP135:BU135"/>
+    <mergeCell ref="BV135:CA135"/>
+    <mergeCell ref="T135:Y135"/>
+    <mergeCell ref="Z135:AE135"/>
+    <mergeCell ref="AF135:AK135"/>
+    <mergeCell ref="AL135:AQ135"/>
+    <mergeCell ref="AR135:AW135"/>
+    <mergeCell ref="BP65:BU65"/>
+    <mergeCell ref="BV65:CA65"/>
+    <mergeCell ref="CB65:CG65"/>
+    <mergeCell ref="CH65:CM65"/>
+    <mergeCell ref="N65:S65"/>
+    <mergeCell ref="AL65:AQ65"/>
+    <mergeCell ref="AR65:AW65"/>
+    <mergeCell ref="AX65:BC65"/>
+    <mergeCell ref="BD65:BI65"/>
+    <mergeCell ref="BJ65:BO65"/>
+    <mergeCell ref="T1:Y1"/>
+    <mergeCell ref="Z1:AE1"/>
+    <mergeCell ref="AF1:AK1"/>
+    <mergeCell ref="T65:Y65"/>
+    <mergeCell ref="Z65:AE65"/>
+    <mergeCell ref="AF65:AK65"/>
     <mergeCell ref="B135:G135"/>
     <mergeCell ref="H135:M135"/>
     <mergeCell ref="CB1:CG1"/>
@@ -35714,35 +37073,6 @@
     <mergeCell ref="AL1:AQ1"/>
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="H1:M1"/>
-    <mergeCell ref="T1:Y1"/>
-    <mergeCell ref="Z1:AE1"/>
-    <mergeCell ref="AF1:AK1"/>
-    <mergeCell ref="T65:Y65"/>
-    <mergeCell ref="Z65:AE65"/>
-    <mergeCell ref="AF65:AK65"/>
-    <mergeCell ref="BP65:BU65"/>
-    <mergeCell ref="BV65:CA65"/>
-    <mergeCell ref="CB65:CG65"/>
-    <mergeCell ref="CH65:CM65"/>
-    <mergeCell ref="N65:S65"/>
-    <mergeCell ref="AL65:AQ65"/>
-    <mergeCell ref="AR65:AW65"/>
-    <mergeCell ref="AX65:BC65"/>
-    <mergeCell ref="BD65:BI65"/>
-    <mergeCell ref="BJ65:BO65"/>
-    <mergeCell ref="CB135:CG135"/>
-    <mergeCell ref="CH135:CM135"/>
-    <mergeCell ref="N135:S135"/>
-    <mergeCell ref="AX135:BC135"/>
-    <mergeCell ref="BD135:BI135"/>
-    <mergeCell ref="BJ135:BO135"/>
-    <mergeCell ref="BP135:BU135"/>
-    <mergeCell ref="BV135:CA135"/>
-    <mergeCell ref="T135:Y135"/>
-    <mergeCell ref="Z135:AE135"/>
-    <mergeCell ref="AF135:AK135"/>
-    <mergeCell ref="AL135:AQ135"/>
-    <mergeCell ref="AR135:AW135"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
